--- a/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_38.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_38.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3451220.487687106</v>
+        <v>3451301.399396715</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17635050.17711724</v>
+        <v>17635050.17711725</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17635050.17711724</v>
+        <v>17635050.17711725</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4819334.840909646</v>
+        <v>4819334.840909678</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4819334.840909646</v>
+        <v>4819334.840909678</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50081623.86100794</v>
+        <v>50081623.86100791</v>
       </c>
     </row>
   </sheetData>
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -708,19 +708,19 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>6.709767317193559</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>134</v>
       </c>
       <c r="X2" t="n">
-        <v>134</v>
+        <v>128.5334307719068</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="D3" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>23.65346312809294</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>114.8712650904796</v>
+        <v>4.524728218572633</v>
       </c>
       <c r="R3" t="n">
         <v>118.9617972923793</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>60.7051195992712</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>112.6835015011931</v>
@@ -854,10 +854,10 @@
         <v>134</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="Q4" t="n">
-        <v>78.63857889953567</v>
+        <v>5.343698498806922</v>
       </c>
       <c r="R4" t="n">
         <v>134</v>
@@ -900,10 +900,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
         <v>2.905110980483547</v>
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>115.1220890195164</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>134</v>
@@ -957,7 +957,7 @@
         <v>134</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>105.869170704636</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>23.65346312809297</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>114.8712650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>118.9617972923793</v>
+        <v>134</v>
       </c>
       <c r="S6" t="n">
-        <v>58.0939999646113</v>
+        <v>134</v>
       </c>
       <c r="T6" t="n">
-        <v>3.519765217513816</v>
+        <v>134</v>
       </c>
       <c r="U6" t="n">
         <v>0.1803597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>65.61095788459721</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>60.70511959927121</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>112.6835015011931</v>
       </c>
       <c r="O7" t="n">
         <v>134</v>
@@ -1094,10 +1094,10 @@
         <v>134</v>
       </c>
       <c r="Q7" t="n">
-        <v>134</v>
+        <v>78.63857889953567</v>
       </c>
       <c r="R7" t="n">
-        <v>118.0272</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1134,13 +1134,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>7.339155739849787</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1179,22 +1179,22 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>72.42726327970983</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>179.9448078592171</v>
       </c>
       <c r="U8" t="n">
-        <v>191</v>
+        <v>179.2879921407383</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>191.0000000000223</v>
       </c>
       <c r="W8" t="n">
-        <v>97.986821345675</v>
+        <v>191.0000000000223</v>
       </c>
       <c r="X8" t="n">
-        <v>189.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1207,20 +1207,20 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>191</v>
       </c>
-      <c r="E9" t="n">
-        <v>191</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>15.03942288827967</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>114.8712650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>115.9617972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>55.0939999646113</v>
+        <v>55.09399996461133</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5197652175138161</v>
+        <v>0.5197652175137932</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>29.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>16.86273944538755</v>
+        <v>146.7734274241469</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>57.7051195992712</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>168.2327999999999</v>
+        <v>183.4098919478674</v>
       </c>
       <c r="P10" t="n">
         <v>191</v>
@@ -1334,7 +1334,7 @@
         <v>191</v>
       </c>
       <c r="R10" t="n">
-        <v>191</v>
+        <v>118.1177884528613</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>174.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>142.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>103.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F11" t="n">
-        <v>97.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>95.90511098048354</v>
@@ -1428,13 +1428,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>131.7362762170029</v>
+        <v>185.1307616080706</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>204.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>153.7051195992712</v>
       </c>
       <c r="N13" t="n">
         <v>205.6835015011931</v>
@@ -1568,10 +1568,10 @@
         <v>328</v>
       </c>
       <c r="Q13" t="n">
-        <v>83.09788750382164</v>
+        <v>257.3927679045504</v>
       </c>
       <c r="R13" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>48.71111904711773</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>92.2814375979998</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,25 +1653,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>168.4272632797098</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>102.3801192051235</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>328.0000000000815</v>
       </c>
       <c r="V14" t="n">
         <v>322.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>328.0000000000675</v>
       </c>
       <c r="X14" t="n">
         <v>285.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>204.3174326828064</v>
+        <v>8.769542372359261</v>
       </c>
     </row>
     <row r="15">
@@ -1699,10 +1699,10 @@
         <v>18.28353587502733</v>
       </c>
       <c r="H15" t="n">
-        <v>22.82250402807275</v>
+        <v>20.76408718642114</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.058416841651614</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1790,28 +1790,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>59.71077569876275</v>
       </c>
       <c r="M16" t="n">
         <v>153.7051195992712</v>
       </c>
       <c r="N16" t="n">
-        <v>205.6835015011931</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>279.4098919478674</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="Q16" t="n">
         <v>328</v>
       </c>
       <c r="R16" t="n">
-        <v>306.1038869516681</v>
+        <v>75.36549370698076</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>48.71111904711773</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1839,22 +1839,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>76.31704439332718</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>61.47457824299391</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>22.33915573984979</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>16.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>14.90511098048353</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>87.42726327970985</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>194.9448078592171</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>261.1531156440881</v>
@@ -1908,7 +1908,7 @@
         <v>204.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>32.87087960854564</v>
+        <v>123.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>120.5354212083766</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>201.4263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1963,28 +1963,28 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>114.8712650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>130.9617972923793</v>
+        <v>328</v>
       </c>
       <c r="S18" t="n">
-        <v>102.5061107359119</v>
+        <v>70.09399996461133</v>
       </c>
       <c r="T18" t="n">
-        <v>328</v>
+        <v>15.51976521751379</v>
       </c>
       <c r="U18" t="n">
         <v>12.18035976018678</v>
       </c>
       <c r="V18" t="n">
+        <v>26.51066719152016</v>
+      </c>
+      <c r="W18" t="n">
+        <v>44.37314290982852</v>
+      </c>
+      <c r="X18" t="n">
         <v>328</v>
-      </c>
-      <c r="W18" t="n">
-        <v>328</v>
-      </c>
-      <c r="X18" t="n">
-        <v>31.86273944538755</v>
       </c>
       <c r="Y18" t="n">
         <v>11.39139276613435</v>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>72.7051195992712</v>
+        <v>69.35794432410968</v>
       </c>
       <c r="N19" t="n">
         <v>124.6835015011931</v>
@@ -2039,7 +2039,7 @@
         <v>198.4098919478674</v>
       </c>
       <c r="P19" t="n">
-        <v>249.8638695940996</v>
+        <v>253.2110448692611</v>
       </c>
       <c r="Q19" t="n">
         <v>305.8272664255981</v>
@@ -2076,25 +2076,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61.42207749846129</v>
+        <v>93.99931295557451</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>61.47457824299391</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>22.33915573984979</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>16.36328960686865</v>
       </c>
       <c r="F20" t="n">
-        <v>16.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>14.90511098048353</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>11.2814375979998</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>87.42726327970985</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>194.9448078592171</v>
       </c>
       <c r="U20" t="n">
-        <v>261.1531156440881</v>
+        <v>187.2749219870567</v>
       </c>
       <c r="V20" t="n">
         <v>241.8510241668239</v>
@@ -2145,7 +2145,7 @@
         <v>204.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>123.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2158,13 +2158,13 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>274.2444482660171</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>327.7640871864211</v>
       </c>
       <c r="I21" t="n">
-        <v>201.4263858913485</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2215,10 +2215,10 @@
         <v>12.18035976018678</v>
       </c>
       <c r="V21" t="n">
-        <v>143.7018724760173</v>
+        <v>26.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>328</v>
+        <v>44.37314290982852</v>
       </c>
       <c r="X21" t="n">
         <v>31.86273944538755</v>
@@ -2273,10 +2273,10 @@
         <v>124.6835015011931</v>
       </c>
       <c r="O22" t="n">
-        <v>198.4098919478674</v>
+        <v>195.0627166727059</v>
       </c>
       <c r="P22" t="n">
-        <v>249.8638695940996</v>
+        <v>253.2110448692611</v>
       </c>
       <c r="Q22" t="n">
         <v>305.8272664255981</v>
@@ -2364,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>19.549796373667</v>
+        <v>90.42726327970983</v>
       </c>
       <c r="T23" t="n">
         <v>197.9448078592171</v>
       </c>
       <c r="U23" t="n">
-        <v>264.1531156440881</v>
+        <v>193.2756487380454</v>
       </c>
       <c r="V23" t="n">
         <v>244.8510241668239</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>156.1562937713393</v>
       </c>
       <c r="C24" t="n">
         <v>361.0999124455193</v>
@@ -2401,10 +2401,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>29.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>200.493581797132</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X24" t="n">
         <v>34.86273944538755</v>
@@ -2553,22 +2553,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>142.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>103.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>97.88962870801186</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>92.28143759799977</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,16 +2601,16 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>168.4272632797098</v>
+        <v>58.57221206085936</v>
       </c>
       <c r="T26" t="n">
         <v>275.9448078592172</v>
       </c>
       <c r="U26" t="n">
-        <v>328.0000000000214</v>
+        <v>328.0000000002193</v>
       </c>
       <c r="V26" t="n">
-        <v>254.7165948782077</v>
+        <v>322.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>20.76408718642113</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2.058416841651483</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.058416841651546</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>211.9617972923793</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>59.71077569876277</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>153.7051195992712</v>
@@ -2750,10 +2750,10 @@
         <v>279.4098919478674</v>
       </c>
       <c r="P28" t="n">
-        <v>328.0000000000214</v>
+        <v>328.0000000002306</v>
       </c>
       <c r="Q28" t="n">
-        <v>197.6819922057662</v>
+        <v>257.3927679043198</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2796,16 +2796,16 @@
         <v>103.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>33.69574309207752</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F29" t="n">
         <v>97.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>95.90511098048353</v>
+        <v>95.90511098048354</v>
       </c>
       <c r="H29" t="n">
-        <v>92.2814375979998</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2850,10 +2850,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>328.0000000002026</v>
+        <v>71.33205762274365</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>285.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>204.3174326828064</v>
@@ -2881,13 +2881,13 @@
         <v>32.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>18.28353587502733</v>
+        <v>18.28353587502734</v>
       </c>
       <c r="H30" t="n">
-        <v>20.76408718642114</v>
+        <v>20.76408718642113</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2.058416841651483</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.058416841651546</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>211.9617972923793</v>
@@ -2920,10 +2920,10 @@
         <v>151.0939999646113</v>
       </c>
       <c r="T30" t="n">
-        <v>96.51976521751379</v>
+        <v>96.51976521751382</v>
       </c>
       <c r="U30" t="n">
-        <v>93.18035976018678</v>
+        <v>93.18035976018675</v>
       </c>
       <c r="V30" t="n">
         <v>107.5106671915202</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>59.71077569876275</v>
+        <v>59.71077569876277</v>
       </c>
       <c r="M31" t="n">
         <v>153.7051195992712</v>
@@ -2990,10 +2990,10 @@
         <v>149.091884153121</v>
       </c>
       <c r="Q31" t="n">
-        <v>328.0000000002617</v>
+        <v>328.0000000002618</v>
       </c>
       <c r="R31" t="n">
-        <v>328.0000000002724</v>
+        <v>328.0000000002723</v>
       </c>
       <c r="S31" t="n">
         <v>48.71111904711773</v>
@@ -3027,7 +3027,7 @@
         <v>58.99931295557451</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>26.47457824299391</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>159.9448078592171</v>
       </c>
       <c r="U32" t="n">
-        <v>226.1531156440881</v>
+        <v>74.02707137125898</v>
       </c>
       <c r="V32" t="n">
         <v>206.8510241668239</v>
@@ -3090,7 +3090,7 @@
         <v>215.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>43.63036743083256</v>
+        <v>169.2818334606677</v>
       </c>
       <c r="Y32" t="n">
         <v>88.31743268280638</v>
@@ -3112,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>271.0000000000205</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>271.0000000000205</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3151,10 +3151,10 @@
         <v>114.8712650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>271.0000000000205</v>
+        <v>95.96179729237929</v>
       </c>
       <c r="S33" t="n">
-        <v>271.0000000000205</v>
+        <v>35.09399996461133</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>271.0000000000205</v>
+        <v>254.3965947426601</v>
       </c>
       <c r="W33" t="n">
         <v>9.373142909828516</v>
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>114.4523919996303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3230,7 +3230,7 @@
         <v>270.8272664255981</v>
       </c>
       <c r="R34" t="n">
-        <v>271.0000000004038</v>
+        <v>271</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3318,16 +3318,16 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>78.23587611856603</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>134.0000000000296</v>
       </c>
       <c r="W35" t="n">
+        <v>78.23587611856603</v>
+      </c>
+      <c r="X35" t="n">
         <v>134.0000000000296</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>88.31743268280638</v>
@@ -3346,22 +3346,22 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
         <v>134.0000000000296</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>134.0000000000296</v>
+        <v>31.82099470725343</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>114.8712650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>108.6540570900827</v>
+        <v>95.96179729237929</v>
       </c>
       <c r="S36" t="n">
         <v>134.0000000000296</v>
@@ -3452,22 +3452,22 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>37.7051195992712</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>89.68350150119306</v>
       </c>
       <c r="O37" t="n">
-        <v>134.0000000000296</v>
+        <v>28.34369849871813</v>
       </c>
       <c r="P37" t="n">
         <v>134.0000000000296</v>
       </c>
       <c r="Q37" t="n">
-        <v>124.6385788994766</v>
+        <v>134.0000000000296</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>134.0000000000296</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>58.99931295557451</v>
       </c>
       <c r="C38" t="n">
         <v>26.47457824299391</v>
@@ -3549,22 +3549,22 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>52.42726327970985</v>
+        <v>52.42726327970983</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>134.0000000005147</v>
       </c>
       <c r="U38" t="n">
-        <v>134.0000000005176</v>
+        <v>25.80861283837158</v>
       </c>
       <c r="V38" t="n">
-        <v>84.80792579356743</v>
+        <v>134.0000000000291</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>134.0000000004047</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>88.31743268280638</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>130.7269947426721</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>114.8712650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>95.96179729237929</v>
+        <v>134.0000000000291</v>
       </c>
       <c r="S39" t="n">
-        <v>35.09399996461133</v>
+        <v>127.7827919996336</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -3689,22 +3689,22 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>37.7051195992712</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>89.68350150119306</v>
+        <v>89.68350150119309</v>
       </c>
       <c r="O40" t="n">
         <v>134.0000000005432</v>
       </c>
       <c r="P40" t="n">
-        <v>124.6385788984603</v>
+        <v>134.00000000054</v>
       </c>
       <c r="Q40" t="n">
         <v>134.0000000005323</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>28.34369849719136</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>134.0000000000528</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>134.0000000000528</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>118.0271999992143</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>134.0000000006801</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,16 +3786,16 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>134.0000000006831</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>134.0000000006667</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>118.0271999981036</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>134.0000000005465</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>119.3172782322709</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>128.2835358750274</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>130.7640871864211</v>
       </c>
       <c r="I42" t="n">
         <v>4.426385891348531</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>134.0000000007159</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>134.00000000069</v>
       </c>
       <c r="U42" t="n">
-        <v>134.0000000006632</v>
+        <v>116.8367269208244</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.401921421387927</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>134.0000000007169</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3932,10 +3932,10 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>134.0000000007491</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.401921421355829</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3975,67 +3975,67 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>118.0271999997543</v>
       </c>
-      <c r="D44" t="n">
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
         <v>134.0000000000819</v>
       </c>
-      <c r="E44" t="n">
+      <c r="V44" t="n">
         <v>134.0000000000819</v>
       </c>
-      <c r="F44" t="n">
+      <c r="W44" t="n">
         <v>134.0000000000819</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -4066,13 +4066,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>128.2835358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>130.7640871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>4.426385891348531</v>
+        <v>4.426385891348517</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4114,13 +4114,13 @@
         <v>134.0000000000819</v>
       </c>
       <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>119.3172782334604</v>
+      </c>
+      <c r="Y45" t="n">
         <v>134.0000000000819</v>
-      </c>
-      <c r="X45" t="n">
-        <v>116.8367269220665</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4136,19 +4136,19 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>4.410970456144607</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>83.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>77.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>28.37217528194649</v>
+        <v>28.37217528194648</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4178,13 +4178,13 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.401921422051501</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>134.0000000000819</v>
       </c>
       <c r="T46" t="n">
-        <v>11.39112388330689</v>
+        <v>11.3911238833069</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>2.170310216216194</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>29.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.72</v>
+        <v>75.5452763532448</v>
       </c>
       <c r="C2" t="n">
-        <v>10.72</v>
+        <v>25.57095489567519</v>
       </c>
       <c r="D2" t="n">
-        <v>10.72</v>
+        <v>15.12736323926126</v>
       </c>
       <c r="E2" t="n">
         <v>10.72</v>
@@ -4333,13 +4333,13 @@
         <v>287.6254165811796</v>
       </c>
       <c r="N2" t="n">
-        <v>342.3384237357115</v>
+        <v>287.6254165811796</v>
       </c>
       <c r="O2" t="n">
-        <v>414.9535106463047</v>
+        <v>360.2405034917729</v>
       </c>
       <c r="P2" t="n">
-        <v>536</v>
+        <v>481.2869928454681</v>
       </c>
       <c r="Q2" t="n">
         <v>536</v>
@@ -4351,22 +4351,22 @@
         <v>536</v>
       </c>
       <c r="T2" t="n">
-        <v>529.22245725536</v>
+        <v>536</v>
       </c>
       <c r="U2" t="n">
-        <v>529.22245725536</v>
+        <v>536</v>
       </c>
       <c r="V2" t="n">
-        <v>393.8689219018247</v>
+        <v>536</v>
       </c>
       <c r="W2" t="n">
-        <v>258.5153865482893</v>
+        <v>400.6464646464647</v>
       </c>
       <c r="X2" t="n">
-        <v>123.1618511947539</v>
+        <v>270.8147163920134</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.72</v>
+        <v>158.3728651972594</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>169.965922351609</v>
+        <v>146.0735353535354</v>
       </c>
       <c r="C3" t="n">
-        <v>169.965922351609</v>
+        <v>10.72</v>
       </c>
       <c r="D3" t="n">
-        <v>34.61238699807367</v>
+        <v>10.72</v>
       </c>
       <c r="E3" t="n">
-        <v>34.61238699807367</v>
+        <v>10.72</v>
       </c>
       <c r="F3" t="n">
-        <v>34.61238699807367</v>
+        <v>10.72</v>
       </c>
       <c r="G3" t="n">
-        <v>34.61238699807367</v>
+        <v>10.72</v>
       </c>
       <c r="H3" t="n">
-        <v>34.61238699807367</v>
+        <v>10.72</v>
       </c>
       <c r="I3" t="n">
         <v>10.72</v>
@@ -4403,49 +4403,49 @@
         <v>143.38</v>
       </c>
       <c r="K3" t="n">
-        <v>270.6800000000001</v>
+        <v>276.04</v>
       </c>
       <c r="L3" t="n">
-        <v>270.6800000000001</v>
+        <v>408.6999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>270.6800000000001</v>
+        <v>536</v>
       </c>
       <c r="N3" t="n">
-        <v>403.34</v>
+        <v>536</v>
       </c>
       <c r="O3" t="n">
-        <v>403.34</v>
+        <v>536</v>
       </c>
       <c r="P3" t="n">
         <v>536</v>
       </c>
       <c r="Q3" t="n">
-        <v>419.9684191005256</v>
+        <v>531.4295674559872</v>
       </c>
       <c r="R3" t="n">
-        <v>299.8049874920617</v>
+        <v>411.2661358475233</v>
       </c>
       <c r="S3" t="n">
-        <v>241.1241794469997</v>
+        <v>352.5853278024613</v>
       </c>
       <c r="T3" t="n">
-        <v>237.5688610454706</v>
+        <v>349.0300094009323</v>
       </c>
       <c r="U3" t="n">
-        <v>237.3866794695244</v>
+        <v>348.847827824986</v>
       </c>
       <c r="V3" t="n">
-        <v>222.7294398821303</v>
+        <v>334.190588237592</v>
       </c>
       <c r="W3" t="n">
-        <v>190.0292955287682</v>
+        <v>301.4904438842298</v>
       </c>
       <c r="X3" t="n">
-        <v>169.965922351609</v>
+        <v>281.4270707070707</v>
       </c>
       <c r="Y3" t="n">
-        <v>169.965922351609</v>
+        <v>281.4270707070707</v>
       </c>
     </row>
     <row r="4">
@@ -4455,49 +4455,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.99988328306451</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="C4" t="n">
-        <v>32.99988328306451</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="D4" t="n">
-        <v>146.3190274080646</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="E4" t="n">
-        <v>146.3190274080646</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="F4" t="n">
-        <v>270.6800000000001</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="G4" t="n">
-        <v>270.6800000000001</v>
+        <v>187.2259921433534</v>
       </c>
       <c r="H4" t="n">
-        <v>403.34</v>
+        <v>319.8859921433534</v>
       </c>
       <c r="I4" t="n">
-        <v>536</v>
+        <v>370.3836679417751</v>
       </c>
       <c r="J4" t="n">
-        <v>536</v>
+        <v>370.3836679417751</v>
       </c>
       <c r="K4" t="n">
-        <v>536</v>
+        <v>503.0436679417751</v>
       </c>
       <c r="L4" t="n">
         <v>536</v>
       </c>
       <c r="M4" t="n">
-        <v>474.6816973744735</v>
+        <v>536</v>
       </c>
       <c r="N4" t="n">
-        <v>360.8599786863997</v>
+        <v>422.1782813119262</v>
       </c>
       <c r="O4" t="n">
-        <v>225.5064433328643</v>
+        <v>286.8247459583908</v>
       </c>
       <c r="P4" t="n">
-        <v>225.5064433328643</v>
+        <v>151.4712106048555</v>
       </c>
       <c r="Q4" t="n">
         <v>146.0735353535354</v>
@@ -4506,25 +4506,25 @@
         <v>10.72</v>
       </c>
       <c r="S4" t="n">
-        <v>10.72</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="T4" t="n">
-        <v>10.72</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="U4" t="n">
-        <v>10.72</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="V4" t="n">
-        <v>10.72</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="W4" t="n">
-        <v>10.72</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="X4" t="n">
-        <v>32.99988328306451</v>
+        <v>54.56599214335344</v>
       </c>
       <c r="Y4" t="n">
-        <v>32.99988328306451</v>
+        <v>54.56599214335344</v>
       </c>
     </row>
     <row r="5">
@@ -4534,16 +4534,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.65445553584197</v>
+        <v>23.0008376720849</v>
       </c>
       <c r="C5" t="n">
-        <v>13.65445553584197</v>
+        <v>23.0008376720849</v>
       </c>
       <c r="D5" t="n">
-        <v>13.65445553584197</v>
+        <v>23.0008376720849</v>
       </c>
       <c r="E5" t="n">
-        <v>13.65445553584197</v>
+        <v>18.59347443282364</v>
       </c>
       <c r="F5" t="n">
         <v>13.65445553584197</v>
@@ -4558,13 +4558,13 @@
         <v>10.72</v>
       </c>
       <c r="J5" t="n">
-        <v>102.3516979065658</v>
+        <v>47.63869075203395</v>
       </c>
       <c r="K5" t="n">
-        <v>209.6784237357115</v>
+        <v>154.9654165811797</v>
       </c>
       <c r="L5" t="n">
-        <v>342.3384237357115</v>
+        <v>287.6254165811796</v>
       </c>
       <c r="M5" t="n">
         <v>342.3384237357115</v>
@@ -4588,22 +4588,22 @@
         <v>536</v>
       </c>
       <c r="T5" t="n">
-        <v>419.7150615964481</v>
+        <v>536</v>
       </c>
       <c r="U5" t="n">
-        <v>284.3615262429127</v>
+        <v>400.6464646464647</v>
       </c>
       <c r="V5" t="n">
-        <v>149.0079908893773</v>
+        <v>265.2929292929293</v>
       </c>
       <c r="W5" t="n">
-        <v>13.65445553584197</v>
+        <v>129.939393939394</v>
       </c>
       <c r="X5" t="n">
-        <v>13.65445553584197</v>
+        <v>23.0008376720849</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.65445553584197</v>
+        <v>23.0008376720849</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.6123869980737</v>
+        <v>10.72</v>
       </c>
       <c r="C6" t="n">
-        <v>34.6123869980737</v>
+        <v>10.72</v>
       </c>
       <c r="D6" t="n">
-        <v>34.6123869980737</v>
+        <v>10.72</v>
       </c>
       <c r="E6" t="n">
         <v>10.72</v>
@@ -4646,10 +4646,10 @@
         <v>10.72</v>
       </c>
       <c r="M6" t="n">
-        <v>138.0200000000001</v>
+        <v>143.38</v>
       </c>
       <c r="N6" t="n">
-        <v>270.6800000000001</v>
+        <v>276.04</v>
       </c>
       <c r="O6" t="n">
         <v>403.34</v>
@@ -4658,31 +4658,31 @@
         <v>536</v>
       </c>
       <c r="Q6" t="n">
-        <v>419.9684191005256</v>
+        <v>536</v>
       </c>
       <c r="R6" t="n">
-        <v>299.8049874920617</v>
+        <v>400.6464646464647</v>
       </c>
       <c r="S6" t="n">
-        <v>241.1241794469998</v>
+        <v>265.2929292929293</v>
       </c>
       <c r="T6" t="n">
-        <v>237.5688610454706</v>
+        <v>129.939393939394</v>
       </c>
       <c r="U6" t="n">
-        <v>237.3866794695244</v>
+        <v>129.7572123634478</v>
       </c>
       <c r="V6" t="n">
-        <v>222.7294398821304</v>
+        <v>63.48351753052128</v>
       </c>
       <c r="W6" t="n">
-        <v>190.0292955287682</v>
+        <v>30.78337317715914</v>
       </c>
       <c r="X6" t="n">
-        <v>169.9659223516091</v>
+        <v>10.72</v>
       </c>
       <c r="Y6" t="n">
-        <v>34.6123869980737</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="7">
@@ -4710,13 +4710,13 @@
         <v>366.2290209283486</v>
       </c>
       <c r="H7" t="n">
+        <v>366.2290209283486</v>
+      </c>
+      <c r="I7" t="n">
+        <v>366.2290209283486</v>
+      </c>
+      <c r="J7" t="n">
         <v>370.3836679417751</v>
-      </c>
-      <c r="I7" t="n">
-        <v>503.0436679417751</v>
-      </c>
-      <c r="J7" t="n">
-        <v>503.0436679417751</v>
       </c>
       <c r="K7" t="n">
         <v>503.0436679417751</v>
@@ -4725,19 +4725,19 @@
         <v>536</v>
       </c>
       <c r="M7" t="n">
-        <v>536</v>
+        <v>474.6816973744735</v>
       </c>
       <c r="N7" t="n">
-        <v>536</v>
+        <v>360.8599786863997</v>
       </c>
       <c r="O7" t="n">
-        <v>400.6464646464647</v>
+        <v>225.5064433328643</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2929292929293</v>
+        <v>90.15290797932897</v>
       </c>
       <c r="Q7" t="n">
-        <v>129.939393939394</v>
+        <v>10.72</v>
       </c>
       <c r="R7" t="n">
         <v>10.72</v>
@@ -4771,16 +4771,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25.97906470174777</v>
+        <v>15.28</v>
       </c>
       <c r="C8" t="n">
-        <v>25.97906470174777</v>
+        <v>15.28</v>
       </c>
       <c r="D8" t="n">
-        <v>18.56577607563687</v>
+        <v>15.28</v>
       </c>
       <c r="E8" t="n">
-        <v>17.18871586667864</v>
+        <v>15.28</v>
       </c>
       <c r="F8" t="n">
         <v>15.28</v>
@@ -4822,25 +4822,25 @@
         <v>764</v>
       </c>
       <c r="S8" t="n">
-        <v>690.8411482023133</v>
+        <v>764</v>
       </c>
       <c r="T8" t="n">
-        <v>509.0787160212859</v>
+        <v>582.2375678189726</v>
       </c>
       <c r="U8" t="n">
-        <v>316.149423091993</v>
+        <v>401.1385858586309</v>
       </c>
       <c r="V8" t="n">
-        <v>316.149423091993</v>
+        <v>208.2092929293154</v>
       </c>
       <c r="W8" t="n">
-        <v>217.1728358741394</v>
+        <v>15.28</v>
       </c>
       <c r="X8" t="n">
-        <v>25.97906470174777</v>
+        <v>15.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>25.97906470174777</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>416.3299221093735</v>
+        <v>208.209292929293</v>
       </c>
       <c r="C9" t="n">
-        <v>416.3299221093735</v>
+        <v>208.209292929293</v>
       </c>
       <c r="D9" t="n">
-        <v>223.4006291800805</v>
+        <v>208.209292929293</v>
       </c>
       <c r="E9" t="n">
-        <v>30.47133625078754</v>
+        <v>208.209292929293</v>
       </c>
       <c r="F9" t="n">
-        <v>30.47133625078754</v>
+        <v>15.28</v>
       </c>
       <c r="G9" t="n">
-        <v>30.47133625078754</v>
+        <v>15.28</v>
       </c>
       <c r="H9" t="n">
-        <v>30.47133625078754</v>
+        <v>15.28</v>
       </c>
       <c r="I9" t="n">
         <v>15.28</v>
@@ -4880,13 +4880,13 @@
         <v>370.977700175299</v>
       </c>
       <c r="L9" t="n">
+        <v>370.977700175299</v>
+      </c>
+      <c r="M9" t="n">
         <v>385.8199999999999</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>574.91</v>
-      </c>
-      <c r="N9" t="n">
-        <v>764</v>
       </c>
       <c r="O9" t="n">
         <v>764</v>
@@ -4895,31 +4895,31 @@
         <v>764</v>
       </c>
       <c r="Q9" t="n">
-        <v>647.9684191005257</v>
+        <v>764</v>
       </c>
       <c r="R9" t="n">
-        <v>530.8352905223647</v>
+        <v>646.8668714218391</v>
       </c>
       <c r="S9" t="n">
-        <v>475.1847855076059</v>
+        <v>591.2163664070802</v>
       </c>
       <c r="T9" t="n">
-        <v>474.6597701363798</v>
+        <v>590.6913510358542</v>
       </c>
       <c r="U9" t="n">
-        <v>474.6597701363798</v>
+        <v>590.6913510358542</v>
       </c>
       <c r="V9" t="n">
-        <v>463.0328335792887</v>
+        <v>579.0644144787631</v>
       </c>
       <c r="W9" t="n">
-        <v>433.3629922562296</v>
+        <v>549.3945731557039</v>
       </c>
       <c r="X9" t="n">
-        <v>416.3299221093735</v>
+        <v>401.1385858585859</v>
       </c>
       <c r="Y9" t="n">
-        <v>416.3299221093735</v>
+        <v>401.1385858585859</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>270.6089732532156</v>
+        <v>15.28</v>
       </c>
       <c r="C10" t="n">
-        <v>399.5809790716514</v>
+        <v>15.28</v>
       </c>
       <c r="D10" t="n">
-        <v>515.8701231966514</v>
+        <v>15.28</v>
       </c>
       <c r="E10" t="n">
-        <v>636.6690274080645</v>
+        <v>15.28</v>
       </c>
       <c r="F10" t="n">
-        <v>764</v>
+        <v>142.6109725919355</v>
       </c>
       <c r="G10" t="n">
-        <v>764</v>
+        <v>299.3660106099683</v>
       </c>
       <c r="H10" t="n">
-        <v>764</v>
+        <v>475.2175570808413</v>
       </c>
       <c r="I10" t="n">
-        <v>764</v>
+        <v>664.3075570808413</v>
       </c>
       <c r="J10" t="n">
-        <v>764</v>
+        <v>728.0736679417752</v>
       </c>
       <c r="K10" t="n">
-        <v>764</v>
+        <v>728.0736679417752</v>
       </c>
       <c r="L10" t="n">
         <v>764</v>
       </c>
       <c r="M10" t="n">
-        <v>764</v>
+        <v>705.7120004047765</v>
       </c>
       <c r="N10" t="n">
-        <v>764</v>
+        <v>705.7120004047765</v>
       </c>
       <c r="O10" t="n">
-        <v>594.0678787878788</v>
+        <v>520.4494832857185</v>
       </c>
       <c r="P10" t="n">
-        <v>401.1385858585859</v>
+        <v>327.5201903564256</v>
       </c>
       <c r="Q10" t="n">
-        <v>208.209292929293</v>
+        <v>134.5908974271326</v>
       </c>
       <c r="R10" t="n">
         <v>15.28</v>
@@ -4983,22 +4983,22 @@
         <v>15.28</v>
       </c>
       <c r="T10" t="n">
-        <v>41.50233490789121</v>
+        <v>15.28</v>
       </c>
       <c r="U10" t="n">
-        <v>41.50233490789121</v>
+        <v>15.28</v>
       </c>
       <c r="V10" t="n">
-        <v>41.50233490789121</v>
+        <v>15.28</v>
       </c>
       <c r="W10" t="n">
-        <v>41.50233490789121</v>
+        <v>15.28</v>
       </c>
       <c r="X10" t="n">
-        <v>41.50233490789121</v>
+        <v>15.28</v>
       </c>
       <c r="Y10" t="n">
-        <v>155.8816355869235</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="11">
@@ -5008,16 +5008,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>221.9922623116115</v>
+        <v>469.7573076466625</v>
       </c>
       <c r="C11" t="n">
-        <v>221.9922623116115</v>
+        <v>325.843592249699</v>
       </c>
       <c r="D11" t="n">
-        <v>221.9922623116115</v>
+        <v>221.4606066538911</v>
       </c>
       <c r="E11" t="n">
-        <v>221.9922623116115</v>
+        <v>123.1138494752359</v>
       </c>
       <c r="F11" t="n">
         <v>123.1138494752359</v>
@@ -5035,13 +5035,13 @@
         <v>350.96</v>
       </c>
       <c r="K11" t="n">
-        <v>675.6800000000001</v>
+        <v>458.2867258291457</v>
       </c>
       <c r="L11" t="n">
-        <v>1000.4</v>
+        <v>783.0067258291458</v>
       </c>
       <c r="M11" t="n">
-        <v>1000.4</v>
+        <v>1107.726725829146</v>
       </c>
       <c r="N11" t="n">
         <v>1118.338423735712</v>
@@ -5071,13 +5071,13 @@
         <v>863.1393220818918</v>
       </c>
       <c r="W11" t="n">
-        <v>531.8261907687604</v>
+        <v>863.1393220818918</v>
       </c>
       <c r="X11" t="n">
-        <v>398.7592450950201</v>
+        <v>676.1385527808104</v>
       </c>
       <c r="Y11" t="n">
-        <v>398.7592450950201</v>
+        <v>469.7573076466625</v>
       </c>
     </row>
     <row r="12">
@@ -5111,19 +5111,19 @@
         <v>26.24</v>
       </c>
       <c r="J12" t="n">
-        <v>26.24</v>
+        <v>192.847700175299</v>
       </c>
       <c r="K12" t="n">
-        <v>26.24</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="L12" t="n">
-        <v>337.3879691800658</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="M12" t="n">
-        <v>537.853110922925</v>
+        <v>655.4033180125416</v>
       </c>
       <c r="N12" t="n">
-        <v>788.5454155304933</v>
+        <v>906.0956226201099</v>
       </c>
       <c r="O12" t="n">
         <v>1113.265415530493</v>
@@ -5166,31 +5166,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>562.9243644433803</v>
+        <v>557.7600860585795</v>
       </c>
       <c r="C13" t="n">
-        <v>596.8563702618161</v>
+        <v>591.6920918770153</v>
       </c>
       <c r="D13" t="n">
-        <v>618.1055143868161</v>
+        <v>612.9412360020153</v>
       </c>
       <c r="E13" t="n">
-        <v>643.8644185982291</v>
+        <v>638.7001402134283</v>
       </c>
       <c r="F13" t="n">
-        <v>676.1553911901647</v>
+        <v>670.9911128053639</v>
       </c>
       <c r="G13" t="n">
-        <v>737.8704292081975</v>
+        <v>732.7061508233967</v>
       </c>
       <c r="H13" t="n">
-        <v>818.6819756790704</v>
+        <v>813.5176972942696</v>
       </c>
       <c r="I13" t="n">
-        <v>959.1265437954812</v>
+        <v>953.9622654106804</v>
       </c>
       <c r="J13" t="n">
-        <v>1254.898264120064</v>
+        <v>1249.733985735263</v>
       </c>
       <c r="K13" t="n">
         <v>1312</v>
@@ -5199,19 +5199,19 @@
         <v>1312</v>
       </c>
       <c r="M13" t="n">
-        <v>1312</v>
+        <v>1156.74230343508</v>
       </c>
       <c r="N13" t="n">
-        <v>1104.238887372532</v>
+        <v>948.9811908076117</v>
       </c>
       <c r="O13" t="n">
-        <v>822.0066732837772</v>
+        <v>666.7489767188567</v>
       </c>
       <c r="P13" t="n">
-        <v>490.6935419706459</v>
+        <v>335.4358454057254</v>
       </c>
       <c r="Q13" t="n">
-        <v>406.7562818657755</v>
+        <v>75.44315055264418</v>
       </c>
       <c r="R13" t="n">
         <v>75.44315055264418</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>217.8003305099681</v>
+        <v>26.24</v>
       </c>
       <c r="C14" t="n">
-        <v>217.8003305099681</v>
+        <v>26.24</v>
       </c>
       <c r="D14" t="n">
-        <v>217.8003305099681</v>
+        <v>26.24</v>
       </c>
       <c r="E14" t="n">
-        <v>119.4535733313129</v>
+        <v>26.24</v>
       </c>
       <c r="F14" t="n">
-        <v>119.4535733313129</v>
+        <v>26.24</v>
       </c>
       <c r="G14" t="n">
-        <v>119.4535733313129</v>
+        <v>26.24</v>
       </c>
       <c r="H14" t="n">
         <v>26.24</v>
@@ -5269,25 +5269,25 @@
         <v>26.24</v>
       </c>
       <c r="J14" t="n">
-        <v>350.96</v>
+        <v>63.15869075203396</v>
       </c>
       <c r="K14" t="n">
-        <v>458.2867258291457</v>
+        <v>335.7501298663648</v>
       </c>
       <c r="L14" t="n">
-        <v>591.4350196984925</v>
+        <v>468.8984237357116</v>
       </c>
       <c r="M14" t="n">
-        <v>591.4350196984925</v>
+        <v>793.6184237357115</v>
       </c>
       <c r="N14" t="n">
-        <v>916.1550196984924</v>
+        <v>1118.338423735712</v>
       </c>
       <c r="O14" t="n">
-        <v>988.7701066090856</v>
+        <v>1190.953510646305</v>
       </c>
       <c r="P14" t="n">
-        <v>1109.816595962781</v>
+        <v>1312</v>
       </c>
       <c r="Q14" t="n">
         <v>1312</v>
@@ -5296,25 +5296,25 @@
         <v>1312</v>
       </c>
       <c r="S14" t="n">
-        <v>1141.871451232616</v>
+        <v>1312</v>
       </c>
       <c r="T14" t="n">
-        <v>1038.457189409259</v>
+        <v>1312</v>
       </c>
       <c r="U14" t="n">
-        <v>1038.457189409259</v>
+        <v>980.6868686867863</v>
       </c>
       <c r="V14" t="n">
-        <v>712.3450437862047</v>
+        <v>654.5747230637319</v>
       </c>
       <c r="W14" t="n">
-        <v>712.3450437862047</v>
+        <v>323.2615917505323</v>
       </c>
       <c r="X14" t="n">
-        <v>424.181575644116</v>
+        <v>35.0981236084437</v>
       </c>
       <c r="Y14" t="n">
-        <v>217.8003305099681</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="15">
@@ -5342,28 +5342,28 @@
         <v>49.29303437179066</v>
       </c>
       <c r="H15" t="n">
-        <v>26.24</v>
+        <v>28.31920893096123</v>
       </c>
       <c r="I15" t="n">
         <v>26.24</v>
       </c>
       <c r="J15" t="n">
-        <v>26.24</v>
+        <v>192.847700175299</v>
       </c>
       <c r="K15" t="n">
-        <v>211.4025536495724</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="L15" t="n">
-        <v>536.1225536495724</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="M15" t="n">
-        <v>736.5876953924317</v>
+        <v>655.4033180125416</v>
       </c>
       <c r="N15" t="n">
-        <v>987.28</v>
+        <v>906.0956226201099</v>
       </c>
       <c r="O15" t="n">
-        <v>1312</v>
+        <v>1113.265415530493</v>
       </c>
       <c r="P15" t="n">
         <v>1312</v>
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>557.7600860585795</v>
+        <v>562.9243644433803</v>
       </c>
       <c r="C16" t="n">
-        <v>591.6920918770153</v>
+        <v>596.8563702618161</v>
       </c>
       <c r="D16" t="n">
-        <v>612.9412360020153</v>
+        <v>618.1055143868161</v>
       </c>
       <c r="E16" t="n">
-        <v>638.7001402134283</v>
+        <v>643.8644185982291</v>
       </c>
       <c r="F16" t="n">
-        <v>670.9911128053639</v>
+        <v>676.1553911901647</v>
       </c>
       <c r="G16" t="n">
-        <v>732.7061508233967</v>
+        <v>737.8704292081975</v>
       </c>
       <c r="H16" t="n">
-        <v>813.5176972942696</v>
+        <v>818.6819756790704</v>
       </c>
       <c r="I16" t="n">
-        <v>953.9622654106804</v>
+        <v>959.1265437954812</v>
       </c>
       <c r="J16" t="n">
-        <v>1249.733985735263</v>
+        <v>1254.898264120064</v>
       </c>
       <c r="K16" t="n">
         <v>1312</v>
       </c>
       <c r="L16" t="n">
-        <v>1312</v>
+        <v>1251.686085152765</v>
       </c>
       <c r="M16" t="n">
-        <v>1156.74230343508</v>
+        <v>1096.428388587844</v>
       </c>
       <c r="N16" t="n">
-        <v>948.9811908076117</v>
+        <v>1096.428388587844</v>
       </c>
       <c r="O16" t="n">
-        <v>666.7489767188567</v>
+        <v>814.1961744990895</v>
       </c>
       <c r="P16" t="n">
-        <v>666.7489767188567</v>
+        <v>482.8830431859581</v>
       </c>
       <c r="Q16" t="n">
-        <v>335.4358454057254</v>
+        <v>151.5699118728268</v>
       </c>
       <c r="R16" t="n">
-        <v>26.24</v>
+        <v>75.44315055264418</v>
       </c>
       <c r="S16" t="n">
         <v>26.24</v>
       </c>
       <c r="T16" t="n">
-        <v>118.6985089707254</v>
+        <v>123.8627873555262</v>
       </c>
       <c r="U16" t="n">
-        <v>273.2003455434382</v>
+        <v>278.364623928239</v>
       </c>
       <c r="V16" t="n">
-        <v>379.9517384293842</v>
+        <v>385.116016814185</v>
       </c>
       <c r="W16" t="n">
-        <v>459.7726566890616</v>
+        <v>464.9369350738624</v>
       </c>
       <c r="X16" t="n">
-        <v>518.7334477132551</v>
+        <v>523.897726098056</v>
       </c>
       <c r="Y16" t="n">
-        <v>538.0727483922874</v>
+        <v>543.2370267770882</v>
       </c>
     </row>
     <row r="17">
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.24</v>
+        <v>143.0162360316556</v>
       </c>
       <c r="C17" t="n">
-        <v>26.24</v>
+        <v>80.92070245287391</v>
       </c>
       <c r="D17" t="n">
-        <v>26.24</v>
+        <v>58.35589867524786</v>
       </c>
       <c r="E17" t="n">
-        <v>26.24</v>
+        <v>58.35589867524786</v>
       </c>
       <c r="F17" t="n">
-        <v>26.24</v>
+        <v>41.29566765705407</v>
       </c>
       <c r="G17" t="n">
         <v>26.24</v>
@@ -5506,16 +5506,16 @@
         <v>26.24</v>
       </c>
       <c r="J17" t="n">
-        <v>63.15869075203396</v>
+        <v>350.96</v>
       </c>
       <c r="K17" t="n">
-        <v>170.4854165811797</v>
+        <v>458.2867258291457</v>
       </c>
       <c r="L17" t="n">
-        <v>303.6337104505264</v>
+        <v>591.4350196984925</v>
       </c>
       <c r="M17" t="n">
-        <v>628.3537104505264</v>
+        <v>793.6184237357115</v>
       </c>
       <c r="N17" t="n">
         <v>793.6184237357115</v>
@@ -5533,25 +5533,25 @@
         <v>1312</v>
       </c>
       <c r="S17" t="n">
-        <v>1223.689633050798</v>
+        <v>1312</v>
       </c>
       <c r="T17" t="n">
-        <v>1026.775685718256</v>
+        <v>1312</v>
       </c>
       <c r="U17" t="n">
-        <v>762.9846598151362</v>
+        <v>1048.208974096881</v>
       </c>
       <c r="V17" t="n">
-        <v>518.6906960102635</v>
+        <v>803.915010292008</v>
       </c>
       <c r="W17" t="n">
-        <v>265.7881950194075</v>
+        <v>551.0125093011519</v>
       </c>
       <c r="X17" t="n">
-        <v>59.44290869550065</v>
+        <v>344.6672229772451</v>
       </c>
       <c r="Y17" t="n">
-        <v>26.24</v>
+        <v>220.1041596612791</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26.24</v>
+        <v>351.4539465653789</v>
       </c>
       <c r="C18" t="n">
-        <v>26.24</v>
+        <v>351.4539465653789</v>
       </c>
       <c r="D18" t="n">
-        <v>26.24</v>
+        <v>351.4539465653789</v>
       </c>
       <c r="E18" t="n">
-        <v>26.24</v>
+        <v>351.4539465653789</v>
       </c>
       <c r="F18" t="n">
-        <v>26.24</v>
+        <v>351.4539465653789</v>
       </c>
       <c r="G18" t="n">
-        <v>26.24</v>
+        <v>351.4539465653789</v>
       </c>
       <c r="H18" t="n">
-        <v>26.24</v>
+        <v>229.700995849847</v>
       </c>
       <c r="I18" t="n">
         <v>26.24</v>
       </c>
       <c r="J18" t="n">
-        <v>26.24</v>
+        <v>192.847700175299</v>
       </c>
       <c r="K18" t="n">
-        <v>211.4025536495724</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="L18" t="n">
-        <v>536.1225536495724</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="M18" t="n">
-        <v>736.5876953924317</v>
+        <v>655.4033180125416</v>
       </c>
       <c r="N18" t="n">
-        <v>987.28</v>
+        <v>906.0956226201099</v>
       </c>
       <c r="O18" t="n">
-        <v>1312</v>
+        <v>1113.265415530493</v>
       </c>
       <c r="P18" t="n">
         <v>1312</v>
       </c>
       <c r="Q18" t="n">
-        <v>1312</v>
+        <v>1195.968419100526</v>
       </c>
       <c r="R18" t="n">
-        <v>1179.715356270324</v>
+        <v>864.6552877873942</v>
       </c>
       <c r="S18" t="n">
-        <v>1076.173830274453</v>
+        <v>793.85326762112</v>
       </c>
       <c r="T18" t="n">
-        <v>744.8606989613221</v>
+        <v>778.1767370983788</v>
       </c>
       <c r="U18" t="n">
-        <v>732.5573052641637</v>
+        <v>765.8733434012204</v>
       </c>
       <c r="V18" t="n">
-        <v>401.2441739510323</v>
+        <v>739.0948916926142</v>
       </c>
       <c r="W18" t="n">
-        <v>69.9310426379009</v>
+        <v>694.2735352180399</v>
       </c>
       <c r="X18" t="n">
-        <v>37.74645733952964</v>
+        <v>362.9604039049086</v>
       </c>
       <c r="Y18" t="n">
-        <v>26.24</v>
+        <v>351.4539465653789</v>
       </c>
     </row>
     <row r="19">
@@ -5640,31 +5640,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>556.7743397725487</v>
+        <v>606.3230314057784</v>
       </c>
       <c r="C19" t="n">
-        <v>556.7743397725487</v>
+        <v>720.4450372242142</v>
       </c>
       <c r="D19" t="n">
-        <v>658.2134838975488</v>
+        <v>821.8841813492143</v>
       </c>
       <c r="E19" t="n">
-        <v>764.1623881089619</v>
+        <v>927.8330855606273</v>
       </c>
       <c r="F19" t="n">
-        <v>876.6433607008973</v>
+        <v>927.8330855606273</v>
       </c>
       <c r="G19" t="n">
-        <v>1018.54839871893</v>
+        <v>927.8330855606273</v>
       </c>
       <c r="H19" t="n">
-        <v>1179.549945189803</v>
+        <v>927.8330855606273</v>
       </c>
       <c r="I19" t="n">
-        <v>1290.923667941775</v>
+        <v>1148.467653677038</v>
       </c>
       <c r="J19" t="n">
-        <v>1290.923667941775</v>
+        <v>1148.467653677038</v>
       </c>
       <c r="K19" t="n">
         <v>1290.923667941775</v>
@@ -5673,13 +5673,13 @@
         <v>1312</v>
       </c>
       <c r="M19" t="n">
-        <v>1238.560485253262</v>
+        <v>1241.941470379687</v>
       </c>
       <c r="N19" t="n">
-        <v>1112.617554443976</v>
+        <v>1115.998539570401</v>
       </c>
       <c r="O19" t="n">
-        <v>912.2035221734025</v>
+        <v>915.5845072998283</v>
       </c>
       <c r="P19" t="n">
         <v>659.8157751086554</v>
@@ -5691,25 +5691,25 @@
         <v>26.24</v>
       </c>
       <c r="S19" t="n">
-        <v>58.20599214335344</v>
+        <v>26.24</v>
       </c>
       <c r="T19" t="n">
-        <v>58.20599214335344</v>
+        <v>26.24</v>
       </c>
       <c r="U19" t="n">
-        <v>58.20599214335344</v>
+        <v>26.24</v>
       </c>
       <c r="V19" t="n">
-        <v>58.20599214335344</v>
+        <v>207.2839844556153</v>
       </c>
       <c r="W19" t="n">
-        <v>218.2169104030309</v>
+        <v>367.2949027152927</v>
       </c>
       <c r="X19" t="n">
-        <v>357.3677014272243</v>
+        <v>506.4456937394862</v>
       </c>
       <c r="Y19" t="n">
-        <v>456.8970021062566</v>
+        <v>506.4456937394862</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>69.75129018837897</v>
+        <v>127.4289127168812</v>
       </c>
       <c r="C20" t="n">
-        <v>69.75129018837897</v>
+        <v>65.33337913809943</v>
       </c>
       <c r="D20" t="n">
-        <v>69.75129018837897</v>
+        <v>42.76857536047338</v>
       </c>
       <c r="E20" t="n">
-        <v>69.75129018837897</v>
+        <v>26.24</v>
       </c>
       <c r="F20" t="n">
-        <v>52.69105917018518</v>
+        <v>26.24</v>
       </c>
       <c r="G20" t="n">
-        <v>37.63539151313111</v>
+        <v>26.24</v>
       </c>
       <c r="H20" t="n">
         <v>26.24</v>
@@ -5743,25 +5743,25 @@
         <v>26.24</v>
       </c>
       <c r="J20" t="n">
-        <v>350.96</v>
+        <v>63.15869075203396</v>
       </c>
       <c r="K20" t="n">
-        <v>529.4117061306532</v>
+        <v>170.4854165811797</v>
       </c>
       <c r="L20" t="n">
-        <v>662.5599999999999</v>
+        <v>303.6337104505264</v>
       </c>
       <c r="M20" t="n">
-        <v>662.5599999999999</v>
+        <v>468.8984237357116</v>
       </c>
       <c r="N20" t="n">
-        <v>662.5599999999999</v>
+        <v>793.6184237357115</v>
       </c>
       <c r="O20" t="n">
+        <v>866.2335106463047</v>
+      </c>
+      <c r="P20" t="n">
         <v>987.28</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1312</v>
       </c>
       <c r="Q20" t="n">
         <v>1312</v>
@@ -5770,25 +5770,25 @@
         <v>1312</v>
       </c>
       <c r="S20" t="n">
-        <v>1223.689633050798</v>
+        <v>1312</v>
       </c>
       <c r="T20" t="n">
-        <v>1223.689633050798</v>
+        <v>1115.086052667457</v>
       </c>
       <c r="U20" t="n">
-        <v>959.8986071476788</v>
+        <v>925.9194648017435</v>
       </c>
       <c r="V20" t="n">
-        <v>715.6046433428062</v>
+        <v>681.6255009968709</v>
       </c>
       <c r="W20" t="n">
-        <v>462.7021423519501</v>
+        <v>428.7230000060148</v>
       </c>
       <c r="X20" t="n">
-        <v>256.3568560280433</v>
+        <v>222.377713682108</v>
       </c>
       <c r="Y20" t="n">
-        <v>131.7937927120772</v>
+        <v>222.377713682108</v>
       </c>
     </row>
     <row r="21">
@@ -5798,40 +5798,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>560.7758313916866</v>
+        <v>965.6425610630689</v>
       </c>
       <c r="C21" t="n">
-        <v>560.7758313916866</v>
+        <v>634.3294297499376</v>
       </c>
       <c r="D21" t="n">
-        <v>560.7758313916866</v>
+        <v>634.3294297499376</v>
       </c>
       <c r="E21" t="n">
-        <v>560.7758313916866</v>
+        <v>357.3148355418396</v>
       </c>
       <c r="F21" t="n">
-        <v>560.7758313916866</v>
+        <v>357.3148355418396</v>
       </c>
       <c r="G21" t="n">
-        <v>560.7758313916866</v>
+        <v>357.3148355418396</v>
       </c>
       <c r="H21" t="n">
-        <v>229.700995849847</v>
+        <v>26.24</v>
       </c>
       <c r="I21" t="n">
         <v>26.24</v>
       </c>
       <c r="J21" t="n">
-        <v>26.24</v>
+        <v>192.847700175299</v>
       </c>
       <c r="K21" t="n">
-        <v>288.3304760943834</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="L21" t="n">
-        <v>613.0504760943834</v>
+        <v>779.6581762696824</v>
       </c>
       <c r="M21" t="n">
-        <v>813.5156178372426</v>
+        <v>980.1233180125416</v>
       </c>
       <c r="N21" t="n">
         <v>987.28</v>
@@ -5858,16 +5858,16 @@
         <v>1080.93341188415</v>
       </c>
       <c r="V21" t="n">
-        <v>935.7800053427188</v>
+        <v>1054.154960175544</v>
       </c>
       <c r="W21" t="n">
-        <v>604.4668740295875</v>
+        <v>1009.33360370097</v>
       </c>
       <c r="X21" t="n">
-        <v>572.2822887312162</v>
+        <v>977.1490184025986</v>
       </c>
       <c r="Y21" t="n">
-        <v>560.7758313916866</v>
+        <v>965.6425610630689</v>
       </c>
     </row>
     <row r="22">
@@ -5877,25 +5877,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1124.25436444338</v>
+        <v>949.4603938655565</v>
       </c>
       <c r="C22" t="n">
-        <v>1238.376370261816</v>
+        <v>949.4603938655565</v>
       </c>
       <c r="D22" t="n">
-        <v>1312</v>
+        <v>949.4603938655565</v>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>949.4603938655565</v>
       </c>
       <c r="F22" t="n">
-        <v>1312</v>
+        <v>949.4603938655565</v>
       </c>
       <c r="G22" t="n">
-        <v>1312</v>
+        <v>1091.365431883589</v>
       </c>
       <c r="H22" t="n">
-        <v>1312</v>
+        <v>1091.365431883589</v>
       </c>
       <c r="I22" t="n">
         <v>1312</v>
@@ -5916,7 +5916,7 @@
         <v>1112.617554443976</v>
       </c>
       <c r="O22" t="n">
-        <v>912.2035221734025</v>
+        <v>915.5845072998283</v>
       </c>
       <c r="P22" t="n">
         <v>659.8157751086554</v>
@@ -5928,25 +5928,25 @@
         <v>26.24</v>
       </c>
       <c r="S22" t="n">
-        <v>26.24</v>
+        <v>58.20599214335344</v>
       </c>
       <c r="T22" t="n">
-        <v>204.0527873555262</v>
+        <v>236.0187794988796</v>
       </c>
       <c r="U22" t="n">
-        <v>438.744623928239</v>
+        <v>463.3572916957397</v>
       </c>
       <c r="V22" t="n">
-        <v>625.686016814185</v>
+        <v>650.2986845816856</v>
       </c>
       <c r="W22" t="n">
-        <v>785.6969350738624</v>
+        <v>810.309602841363</v>
       </c>
       <c r="X22" t="n">
-        <v>924.8477260980559</v>
+        <v>949.4603938655565</v>
       </c>
       <c r="Y22" t="n">
-        <v>1024.377026777088</v>
+        <v>949.4603938655565</v>
       </c>
     </row>
     <row r="23">
@@ -5980,25 +5980,25 @@
         <v>32.4</v>
       </c>
       <c r="J23" t="n">
-        <v>69.31869075203394</v>
+        <v>433.350000000015</v>
       </c>
       <c r="K23" t="n">
-        <v>176.6454165811797</v>
+        <v>540.6767258291607</v>
       </c>
       <c r="L23" t="n">
-        <v>309.7937104505264</v>
+        <v>941.6267258291607</v>
       </c>
       <c r="M23" t="n">
-        <v>624.4384237356815</v>
+        <v>1146.434913089392</v>
       </c>
       <c r="N23" t="n">
-        <v>1025.388423735697</v>
+        <v>1146.434913089392</v>
       </c>
       <c r="O23" t="n">
-        <v>1098.00351064629</v>
+        <v>1219.049999999985</v>
       </c>
       <c r="P23" t="n">
-        <v>1219.049999999985</v>
+        <v>1620</v>
       </c>
       <c r="Q23" t="n">
         <v>1620</v>
@@ -6007,10 +6007,10 @@
         <v>1620</v>
       </c>
       <c r="S23" t="n">
-        <v>1600.25273093569</v>
+        <v>1528.659330020495</v>
       </c>
       <c r="T23" t="n">
-        <v>1400.308480572844</v>
+        <v>1328.71507965765</v>
       </c>
       <c r="U23" t="n">
         <v>1133.487151639422</v>
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1094.733026833469</v>
+        <v>1091.666506748585</v>
       </c>
       <c r="C24" t="n">
-        <v>729.9856405248639</v>
+        <v>726.9191204399793</v>
       </c>
       <c r="D24" t="n">
-        <v>378.5334315372855</v>
+        <v>375.4669114524009</v>
       </c>
       <c r="E24" t="n">
-        <v>32.4</v>
+        <v>375.4669114524009</v>
       </c>
       <c r="F24" t="n">
         <v>32.4</v>
@@ -6071,7 +6071,7 @@
         <v>1030.933679607742</v>
       </c>
       <c r="N24" t="n">
-        <v>1281.62598421531</v>
+        <v>1074.813903846774</v>
       </c>
       <c r="O24" t="n">
         <v>1421.265415530493</v>
@@ -6098,13 +6098,13 @@
         <v>1347.003445024029</v>
       </c>
       <c r="W24" t="n">
-        <v>1144.484675531976</v>
+        <v>1299.151785519151</v>
       </c>
       <c r="X24" t="n">
-        <v>1109.269787203302</v>
+        <v>1263.936897190477</v>
       </c>
       <c r="Y24" t="n">
-        <v>1094.733026833469</v>
+        <v>1249.400136820645</v>
       </c>
     </row>
     <row r="25">
@@ -6114,34 +6114,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>623.0926261198102</v>
+        <v>598.454225681063</v>
       </c>
       <c r="C25" t="n">
-        <v>623.0926261198102</v>
+        <v>598.454225681063</v>
       </c>
       <c r="D25" t="n">
-        <v>721.5617702448103</v>
+        <v>696.9233698060631</v>
       </c>
       <c r="E25" t="n">
-        <v>824.5406744562233</v>
+        <v>696.9233698060631</v>
       </c>
       <c r="F25" t="n">
-        <v>824.5406744562233</v>
+        <v>806.4343423979985</v>
       </c>
       <c r="G25" t="n">
-        <v>824.5406744562233</v>
+        <v>806.4343423979985</v>
       </c>
       <c r="H25" t="n">
-        <v>982.5722209270963</v>
+        <v>964.4658888688715</v>
       </c>
       <c r="I25" t="n">
-        <v>1200.236789043507</v>
+        <v>1182.130456985282</v>
       </c>
       <c r="J25" t="n">
-        <v>1200.236789043507</v>
+        <v>1182.130456985282</v>
       </c>
       <c r="K25" t="n">
-        <v>1339.722803308244</v>
+        <v>1321.616471250019</v>
       </c>
       <c r="L25" t="n">
         <v>1339.722803308244</v>
@@ -6168,22 +6168,22 @@
         <v>61.39599214335344</v>
       </c>
       <c r="T25" t="n">
-        <v>236.2387794988796</v>
+        <v>111.7658780518677</v>
       </c>
       <c r="U25" t="n">
-        <v>467.9606160715924</v>
+        <v>111.7658780518677</v>
       </c>
       <c r="V25" t="n">
-        <v>467.9606160715924</v>
+        <v>111.7658780518677</v>
       </c>
       <c r="W25" t="n">
-        <v>467.9606160715924</v>
+        <v>268.8067963115451</v>
       </c>
       <c r="X25" t="n">
-        <v>526.533325440778</v>
+        <v>404.9875873357386</v>
       </c>
       <c r="Y25" t="n">
-        <v>623.0926261198102</v>
+        <v>501.5468880147709</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>274.5367009927714</v>
+        <v>316.6787433463437</v>
       </c>
       <c r="C26" t="n">
-        <v>130.6229855958079</v>
+        <v>316.6787433463437</v>
       </c>
       <c r="D26" t="n">
-        <v>26.24</v>
+        <v>316.6787433463437</v>
       </c>
       <c r="E26" t="n">
-        <v>26.24</v>
+        <v>218.3319861676885</v>
       </c>
       <c r="F26" t="n">
-        <v>26.24</v>
+        <v>119.4535733313129</v>
       </c>
       <c r="G26" t="n">
-        <v>26.24</v>
+        <v>119.4535733313129</v>
       </c>
       <c r="H26" t="n">
         <v>26.24</v>
@@ -6226,16 +6226,16 @@
         <v>303.6337104505264</v>
       </c>
       <c r="M26" t="n">
-        <v>303.6337104505264</v>
+        <v>628.3537104505476</v>
       </c>
       <c r="N26" t="n">
-        <v>628.3537104505476</v>
+        <v>793.6184237356904</v>
       </c>
       <c r="O26" t="n">
-        <v>953.0737104505688</v>
+        <v>866.2335106462835</v>
       </c>
       <c r="P26" t="n">
-        <v>1074.120199804264</v>
+        <v>987.2799999999788</v>
       </c>
       <c r="Q26" t="n">
         <v>1312</v>
@@ -6244,25 +6244,25 @@
         <v>1312</v>
       </c>
       <c r="S26" t="n">
-        <v>1141.871451232616</v>
+        <v>1252.836149433475</v>
       </c>
       <c r="T26" t="n">
-        <v>863.1393220818918</v>
+        <v>974.104020282751</v>
       </c>
       <c r="U26" t="n">
-        <v>531.8261907687388</v>
+        <v>642.7908889693981</v>
       </c>
       <c r="V26" t="n">
-        <v>274.5367009927714</v>
+        <v>316.6787433463437</v>
       </c>
       <c r="W26" t="n">
-        <v>274.5367009927714</v>
+        <v>316.6787433463437</v>
       </c>
       <c r="X26" t="n">
-        <v>274.5367009927714</v>
+        <v>316.6787433463437</v>
       </c>
       <c r="Y26" t="n">
-        <v>274.5367009927714</v>
+        <v>316.6787433463437</v>
       </c>
     </row>
     <row r="27">
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>230.6779413782423</v>
+        <v>232.7571503092034</v>
       </c>
       <c r="C27" t="n">
-        <v>176.0315651706471</v>
+        <v>178.1107741016082</v>
       </c>
       <c r="D27" t="n">
-        <v>134.6803662840788</v>
+        <v>136.7595752150399</v>
       </c>
       <c r="E27" t="n">
-        <v>98.64794484780339</v>
+        <v>100.7271537787645</v>
       </c>
       <c r="F27" t="n">
-        <v>65.6820434964126</v>
+        <v>67.76125242737371</v>
       </c>
       <c r="G27" t="n">
-        <v>47.21382544082943</v>
+        <v>49.29303437179053</v>
       </c>
       <c r="H27" t="n">
-        <v>26.24</v>
+        <v>28.3192089309611</v>
       </c>
       <c r="I27" t="n">
         <v>26.24</v>
@@ -6299,16 +6299,16 @@
         <v>192.847700175299</v>
       </c>
       <c r="K27" t="n">
-        <v>192.847700175299</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="L27" t="n">
-        <v>517.5677001753202</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="M27" t="n">
-        <v>718.0328419181794</v>
+        <v>537.8531109229039</v>
       </c>
       <c r="N27" t="n">
-        <v>968.7251465257477</v>
+        <v>788.5454155304722</v>
       </c>
       <c r="O27" t="n">
         <v>1113.265415530493</v>
@@ -6317,31 +6317,31 @@
         <v>1312</v>
       </c>
       <c r="Q27" t="n">
-        <v>1309.920791069039</v>
+        <v>1312</v>
       </c>
       <c r="R27" t="n">
-        <v>1095.817965521181</v>
+        <v>1097.897174452142</v>
       </c>
       <c r="S27" t="n">
-        <v>943.197763536725</v>
+        <v>945.2769724676862</v>
       </c>
       <c r="T27" t="n">
-        <v>845.703051195802</v>
+        <v>847.782260126763</v>
       </c>
       <c r="U27" t="n">
-        <v>751.5814756804618</v>
+        <v>753.6606846114229</v>
       </c>
       <c r="V27" t="n">
-        <v>642.9848421536738</v>
+        <v>645.0640510846348</v>
       </c>
       <c r="W27" t="n">
-        <v>516.3453038609176</v>
+        <v>518.4245127918787</v>
       </c>
       <c r="X27" t="n">
-        <v>402.3425367443646</v>
+        <v>404.4217456753256</v>
       </c>
       <c r="Y27" t="n">
-        <v>309.0178975866531</v>
+        <v>311.0971065176142</v>
       </c>
     </row>
     <row r="28">
@@ -6366,34 +6366,34 @@
         <v>676.1553911901647</v>
       </c>
       <c r="G28" t="n">
-        <v>737.8704292081975</v>
+        <v>732.7061508233967</v>
       </c>
       <c r="H28" t="n">
-        <v>818.6819756790704</v>
+        <v>813.5176972942696</v>
       </c>
       <c r="I28" t="n">
-        <v>959.1265437954812</v>
+        <v>953.9622654106804</v>
       </c>
       <c r="J28" t="n">
-        <v>1254.898264120064</v>
+        <v>1249.733985735263</v>
       </c>
       <c r="K28" t="n">
         <v>1312</v>
       </c>
       <c r="L28" t="n">
-        <v>1251.686085152765</v>
+        <v>1312</v>
       </c>
       <c r="M28" t="n">
-        <v>1096.428388587844</v>
+        <v>1156.74230343508</v>
       </c>
       <c r="N28" t="n">
-        <v>888.6672759603766</v>
+        <v>948.9811908076117</v>
       </c>
       <c r="O28" t="n">
-        <v>606.4350618716217</v>
+        <v>666.7489767188567</v>
       </c>
       <c r="P28" t="n">
-        <v>275.1219305584686</v>
+        <v>335.4358454054924</v>
       </c>
       <c r="Q28" t="n">
         <v>75.44315055264418</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.5386407691075</v>
+        <v>568.6357204830381</v>
       </c>
       <c r="C29" t="n">
-        <v>453.6249253721439</v>
+        <v>424.7220050860745</v>
       </c>
       <c r="D29" t="n">
-        <v>349.241939776336</v>
+        <v>320.3390194902667</v>
       </c>
       <c r="E29" t="n">
-        <v>315.2058356429244</v>
+        <v>221.9922623116115</v>
       </c>
       <c r="F29" t="n">
-        <v>216.3274228065488</v>
+        <v>123.1138494752359</v>
       </c>
       <c r="G29" t="n">
-        <v>119.4535733313129</v>
+        <v>26.24</v>
       </c>
       <c r="H29" t="n">
         <v>26.24</v>
@@ -6457,22 +6457,22 @@
         <v>63.15869075203396</v>
       </c>
       <c r="K29" t="n">
-        <v>170.4854165811797</v>
+        <v>335.7501298663224</v>
       </c>
       <c r="L29" t="n">
-        <v>303.6337104505264</v>
+        <v>468.8984237356692</v>
       </c>
       <c r="M29" t="n">
-        <v>468.8984237356692</v>
+        <v>793.6184237356904</v>
       </c>
       <c r="N29" t="n">
-        <v>793.6184237356904</v>
+        <v>1118.338423735712</v>
       </c>
       <c r="O29" t="n">
-        <v>866.2335106462835</v>
+        <v>1190.953510646305</v>
       </c>
       <c r="P29" t="n">
-        <v>987.2799999999788</v>
+        <v>1312</v>
       </c>
       <c r="Q29" t="n">
         <v>1312</v>
@@ -6493,13 +6493,13 @@
         <v>1312</v>
       </c>
       <c r="W29" t="n">
-        <v>980.686868686664</v>
+        <v>1239.947416542683</v>
       </c>
       <c r="X29" t="n">
-        <v>980.686868686664</v>
+        <v>951.7839484005946</v>
       </c>
       <c r="Y29" t="n">
-        <v>774.3056235525161</v>
+        <v>745.4027032664467</v>
       </c>
     </row>
     <row r="30">
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>230.6779413782423</v>
+        <v>232.7571503092034</v>
       </c>
       <c r="C30" t="n">
-        <v>176.0315651706471</v>
+        <v>178.1107741016082</v>
       </c>
       <c r="D30" t="n">
-        <v>134.6803662840788</v>
+        <v>136.7595752150399</v>
       </c>
       <c r="E30" t="n">
-        <v>98.64794484780339</v>
+        <v>100.7271537787645</v>
       </c>
       <c r="F30" t="n">
-        <v>65.6820434964126</v>
+        <v>67.76125242737371</v>
       </c>
       <c r="G30" t="n">
-        <v>47.21382544082944</v>
+        <v>49.29303437179053</v>
       </c>
       <c r="H30" t="n">
-        <v>26.24</v>
+        <v>28.3192089309611</v>
       </c>
       <c r="I30" t="n">
         <v>26.24</v>
@@ -6536,49 +6536,49 @@
         <v>192.847700175299</v>
       </c>
       <c r="K30" t="n">
-        <v>192.847700175299</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="L30" t="n">
-        <v>517.5677001753202</v>
+        <v>454.9381762696823</v>
       </c>
       <c r="M30" t="n">
-        <v>718.0328419181794</v>
+        <v>655.4033180125416</v>
       </c>
       <c r="N30" t="n">
-        <v>968.7251465257477</v>
+        <v>906.0956226201099</v>
       </c>
       <c r="O30" t="n">
-        <v>1293.445146525769</v>
+        <v>1113.265415530493</v>
       </c>
       <c r="P30" t="n">
         <v>1312</v>
       </c>
       <c r="Q30" t="n">
-        <v>1309.920791069039</v>
+        <v>1312</v>
       </c>
       <c r="R30" t="n">
-        <v>1095.817965521181</v>
+        <v>1097.897174452142</v>
       </c>
       <c r="S30" t="n">
-        <v>943.197763536725</v>
+        <v>945.2769724676862</v>
       </c>
       <c r="T30" t="n">
-        <v>845.703051195802</v>
+        <v>847.782260126763</v>
       </c>
       <c r="U30" t="n">
-        <v>751.5814756804618</v>
+        <v>753.6606846114229</v>
       </c>
       <c r="V30" t="n">
-        <v>642.9848421536738</v>
+        <v>645.0640510846348</v>
       </c>
       <c r="W30" t="n">
-        <v>516.3453038609176</v>
+        <v>518.4245127918787</v>
       </c>
       <c r="X30" t="n">
-        <v>402.3425367443646</v>
+        <v>404.4217456753256</v>
       </c>
       <c r="Y30" t="n">
-        <v>309.0178975866531</v>
+        <v>311.0971065176142</v>
       </c>
     </row>
     <row r="31">
@@ -6591,28 +6591,28 @@
         <v>562.9243644433803</v>
       </c>
       <c r="C31" t="n">
-        <v>591.6920918770153</v>
+        <v>596.8563702618161</v>
       </c>
       <c r="D31" t="n">
-        <v>612.9412360020153</v>
+        <v>618.1055143868161</v>
       </c>
       <c r="E31" t="n">
-        <v>638.7001402134283</v>
+        <v>643.8644185982291</v>
       </c>
       <c r="F31" t="n">
-        <v>670.9911128053639</v>
+        <v>676.1553911901647</v>
       </c>
       <c r="G31" t="n">
-        <v>732.7061508233967</v>
+        <v>737.8704292081975</v>
       </c>
       <c r="H31" t="n">
-        <v>813.5176972942696</v>
+        <v>818.6819756790704</v>
       </c>
       <c r="I31" t="n">
-        <v>953.9622654106804</v>
+        <v>959.1265437954812</v>
       </c>
       <c r="J31" t="n">
-        <v>1249.733985735263</v>
+        <v>1254.898264120064</v>
       </c>
       <c r="K31" t="n">
         <v>1312</v>
@@ -6645,13 +6645,13 @@
         <v>123.8627873555262</v>
       </c>
       <c r="U31" t="n">
-        <v>278.364623928239</v>
+        <v>278.3646239282391</v>
       </c>
       <c r="V31" t="n">
-        <v>385.116016814185</v>
+        <v>385.1160168141851</v>
       </c>
       <c r="W31" t="n">
-        <v>464.9369350738624</v>
+        <v>464.9369350738625</v>
       </c>
       <c r="X31" t="n">
         <v>523.897726098056</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21.68</v>
+        <v>48.42199822524638</v>
       </c>
       <c r="C32" t="n">
         <v>21.68</v>
@@ -6700,16 +6700,16 @@
         <v>299.0737104505264</v>
       </c>
       <c r="M32" t="n">
-        <v>353.7584237356708</v>
+        <v>567.3637104505467</v>
       </c>
       <c r="N32" t="n">
-        <v>622.0484237356911</v>
+        <v>835.653710450567</v>
       </c>
       <c r="O32" t="n">
-        <v>694.6635106462844</v>
+        <v>908.2687973611603</v>
       </c>
       <c r="P32" t="n">
-        <v>815.7099999999797</v>
+        <v>1029.315286714856</v>
       </c>
       <c r="Q32" t="n">
         <v>1084</v>
@@ -6724,19 +6724,19 @@
         <v>869.4827564253263</v>
       </c>
       <c r="U32" t="n">
-        <v>641.0452658757424</v>
+        <v>794.7079368583981</v>
       </c>
       <c r="V32" t="n">
-        <v>432.1048374244051</v>
+        <v>585.7675084070607</v>
       </c>
       <c r="W32" t="n">
-        <v>214.5558717870843</v>
+        <v>368.21854276974</v>
       </c>
       <c r="X32" t="n">
-        <v>170.4847935741221</v>
+        <v>197.2267917993685</v>
       </c>
       <c r="Y32" t="n">
-        <v>81.27526561169142</v>
+        <v>108.0172638369378</v>
       </c>
     </row>
     <row r="33">
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.68</v>
+        <v>569.154747474789</v>
       </c>
       <c r="C33" t="n">
-        <v>21.68</v>
+        <v>569.154747474789</v>
       </c>
       <c r="D33" t="n">
-        <v>21.68</v>
+        <v>569.154747474789</v>
       </c>
       <c r="E33" t="n">
-        <v>21.68</v>
+        <v>295.4173737373945</v>
       </c>
       <c r="F33" t="n">
         <v>21.68</v>
@@ -6770,22 +6770,22 @@
         <v>21.68</v>
       </c>
       <c r="J33" t="n">
-        <v>21.68</v>
+        <v>188.287700175299</v>
       </c>
       <c r="K33" t="n">
-        <v>96.26255364953187</v>
+        <v>450.3781762696823</v>
       </c>
       <c r="L33" t="n">
-        <v>364.5525536495522</v>
+        <v>450.3781762696823</v>
       </c>
       <c r="M33" t="n">
-        <v>565.0176953924114</v>
+        <v>650.8433180125414</v>
       </c>
       <c r="N33" t="n">
-        <v>815.7099999999797</v>
+        <v>885.2654155304933</v>
       </c>
       <c r="O33" t="n">
-        <v>1084</v>
+        <v>885.2654155304933</v>
       </c>
       <c r="P33" t="n">
         <v>1084</v>
@@ -6794,28 +6794,28 @@
         <v>967.9684191005257</v>
       </c>
       <c r="R33" t="n">
-        <v>694.2310453631312</v>
+        <v>871.037310724385</v>
       </c>
       <c r="S33" t="n">
-        <v>420.4936716257367</v>
+        <v>835.5888259116463</v>
       </c>
       <c r="T33" t="n">
-        <v>420.4936716257367</v>
+        <v>835.5888259116463</v>
       </c>
       <c r="U33" t="n">
-        <v>420.4936716257367</v>
+        <v>835.5888259116463</v>
       </c>
       <c r="V33" t="n">
-        <v>146.7562978883423</v>
+        <v>578.6225685958279</v>
       </c>
       <c r="W33" t="n">
-        <v>137.2884767673034</v>
+        <v>569.154747474789</v>
       </c>
       <c r="X33" t="n">
-        <v>137.2884767673034</v>
+        <v>569.154747474789</v>
       </c>
       <c r="Y33" t="n">
-        <v>21.68</v>
+        <v>569.154747474789</v>
       </c>
     </row>
     <row r="34">
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>329.6600917032258</v>
+        <v>934.3593319019589</v>
       </c>
       <c r="C34" t="n">
-        <v>478.4320975216616</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="D34" t="n">
-        <v>478.4320975216616</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="E34" t="n">
-        <v>478.4320975216616</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="F34" t="n">
-        <v>478.4320975216616</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="G34" t="n">
-        <v>478.4320975216616</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="H34" t="n">
-        <v>478.4320975216616</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="I34" t="n">
-        <v>733.7166656380724</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="J34" t="n">
-        <v>850.2989913978404</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="K34" t="n">
-        <v>1027.405005662578</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="L34" t="n">
-        <v>1083.131337720803</v>
+        <v>1083.131337720395</v>
       </c>
       <c r="M34" t="n">
-        <v>1045.045358327599</v>
+        <v>1045.045358327191</v>
       </c>
       <c r="N34" t="n">
-        <v>954.4559628718489</v>
+        <v>954.455962871441</v>
       </c>
       <c r="O34" t="n">
-        <v>789.395465954811</v>
+        <v>789.3954659544031</v>
       </c>
       <c r="P34" t="n">
-        <v>568.9802691171736</v>
+        <v>568.9802691167657</v>
       </c>
       <c r="Q34" t="n">
-        <v>295.4173737377816</v>
+        <v>295.4173737373737</v>
       </c>
       <c r="R34" t="n">
         <v>21.68</v>
@@ -6882,19 +6882,19 @@
         <v>21.68</v>
       </c>
       <c r="U34" t="n">
-        <v>21.68</v>
+        <v>289.9700000000203</v>
       </c>
       <c r="V34" t="n">
-        <v>21.68</v>
+        <v>511.5613928859663</v>
       </c>
       <c r="W34" t="n">
-        <v>21.68</v>
+        <v>706.2223111456436</v>
       </c>
       <c r="X34" t="n">
-        <v>195.4807910241935</v>
+        <v>799.8319942356667</v>
       </c>
       <c r="Y34" t="n">
-        <v>329.6600917032258</v>
+        <v>799.8319942356667</v>
       </c>
     </row>
     <row r="35">
@@ -6940,13 +6940,13 @@
         <v>287.6254165811796</v>
       </c>
       <c r="N35" t="n">
-        <v>342.3384237357115</v>
+        <v>287.6254165811796</v>
       </c>
       <c r="O35" t="n">
-        <v>414.9535106463047</v>
+        <v>360.2405034917729</v>
       </c>
       <c r="P35" t="n">
-        <v>536</v>
+        <v>481.2869928454681</v>
       </c>
       <c r="Q35" t="n">
         <v>536</v>
@@ -6961,13 +6961,13 @@
         <v>536</v>
       </c>
       <c r="U35" t="n">
-        <v>456.973862506499</v>
+        <v>536</v>
       </c>
       <c r="V35" t="n">
+        <v>400.6464646464348</v>
+      </c>
+      <c r="W35" t="n">
         <v>321.6203271529337</v>
-      </c>
-      <c r="W35" t="n">
-        <v>186.2667917993685</v>
       </c>
       <c r="X35" t="n">
         <v>186.2667917993685</v>
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>281.4270707071305</v>
+        <v>178.2159542497808</v>
       </c>
       <c r="C36" t="n">
-        <v>281.4270707071305</v>
+        <v>178.2159542497808</v>
       </c>
       <c r="D36" t="n">
-        <v>146.0735353535652</v>
+        <v>178.2159542497808</v>
       </c>
       <c r="E36" t="n">
-        <v>146.0735353535652</v>
+        <v>178.2159542497808</v>
       </c>
       <c r="F36" t="n">
-        <v>146.0735353535652</v>
+        <v>178.2159542497808</v>
       </c>
       <c r="G36" t="n">
-        <v>146.0735353535652</v>
+        <v>42.86241889621559</v>
       </c>
       <c r="H36" t="n">
-        <v>146.0735353535652</v>
+        <v>42.86241889621559</v>
       </c>
       <c r="I36" t="n">
         <v>10.72</v>
       </c>
       <c r="J36" t="n">
-        <v>10.72</v>
+        <v>138.0199999999121</v>
       </c>
       <c r="K36" t="n">
-        <v>143.3800000000293</v>
+        <v>138.0199999999121</v>
       </c>
       <c r="L36" t="n">
-        <v>143.3800000000293</v>
+        <v>270.6799999999414</v>
       </c>
       <c r="M36" t="n">
-        <v>276.0400000000586</v>
+        <v>403.3399999999707</v>
       </c>
       <c r="N36" t="n">
         <v>403.3399999999707</v>
       </c>
       <c r="O36" t="n">
-        <v>403.3399999999707</v>
+        <v>536</v>
       </c>
       <c r="P36" t="n">
         <v>536</v>
       </c>
       <c r="Q36" t="n">
-        <v>536</v>
+        <v>419.9684191005256</v>
       </c>
       <c r="R36" t="n">
-        <v>426.2484271817347</v>
+        <v>323.037310724385</v>
       </c>
       <c r="S36" t="n">
-        <v>290.8948918281694</v>
+        <v>187.6837753708197</v>
       </c>
       <c r="T36" t="n">
-        <v>290.8948918281694</v>
+        <v>187.6837753708197</v>
       </c>
       <c r="U36" t="n">
-        <v>290.8948918281694</v>
+        <v>187.6837753708197</v>
       </c>
       <c r="V36" t="n">
-        <v>290.8948918281694</v>
+        <v>187.6837753708197</v>
       </c>
       <c r="W36" t="n">
-        <v>281.4270707071305</v>
+        <v>178.2159542497808</v>
       </c>
       <c r="X36" t="n">
-        <v>281.4270707071305</v>
+        <v>178.2159542497808</v>
       </c>
       <c r="Y36" t="n">
-        <v>281.4270707071305</v>
+        <v>178.2159542497808</v>
       </c>
     </row>
     <row r="37">
@@ -7062,31 +7062,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>214.9536679417165</v>
+        <v>408.7000000000879</v>
       </c>
       <c r="C37" t="n">
-        <v>214.9536679417165</v>
+        <v>408.7000000000879</v>
       </c>
       <c r="D37" t="n">
-        <v>214.9536679417165</v>
+        <v>408.7000000000879</v>
       </c>
       <c r="E37" t="n">
-        <v>347.6136679417458</v>
+        <v>408.7000000000879</v>
       </c>
       <c r="F37" t="n">
-        <v>347.6136679417458</v>
+        <v>408.7000000000879</v>
       </c>
       <c r="G37" t="n">
-        <v>347.6136679417458</v>
+        <v>480.2736679417751</v>
       </c>
       <c r="H37" t="n">
-        <v>347.6136679417458</v>
+        <v>480.2736679417751</v>
       </c>
       <c r="I37" t="n">
-        <v>347.6136679417458</v>
+        <v>480.2736679417751</v>
       </c>
       <c r="J37" t="n">
-        <v>347.6136679417458</v>
+        <v>480.2736679417751</v>
       </c>
       <c r="K37" t="n">
         <v>480.2736679417751</v>
@@ -7095,43 +7095,43 @@
         <v>536</v>
       </c>
       <c r="M37" t="n">
-        <v>497.9140206067968</v>
+        <v>536</v>
       </c>
       <c r="N37" t="n">
-        <v>407.3246251510462</v>
+        <v>445.4106045442494</v>
       </c>
       <c r="O37" t="n">
-        <v>271.971089797481</v>
+        <v>416.7806060606957</v>
       </c>
       <c r="P37" t="n">
-        <v>136.6175544439158</v>
+        <v>281.4270707071305</v>
       </c>
       <c r="Q37" t="n">
-        <v>10.72</v>
+        <v>146.0735353535652</v>
       </c>
       <c r="R37" t="n">
         <v>10.72</v>
       </c>
       <c r="S37" t="n">
-        <v>77.33599214335344</v>
+        <v>10.72</v>
       </c>
       <c r="T37" t="n">
-        <v>77.33599214335344</v>
+        <v>143.3800000000293</v>
       </c>
       <c r="U37" t="n">
-        <v>82.2936679416872</v>
+        <v>143.3800000000293</v>
       </c>
       <c r="V37" t="n">
-        <v>82.2936679416872</v>
+        <v>276.0400000000586</v>
       </c>
       <c r="W37" t="n">
-        <v>214.9536679417165</v>
+        <v>276.0400000000586</v>
       </c>
       <c r="X37" t="n">
-        <v>214.9536679417165</v>
+        <v>408.7000000000879</v>
       </c>
       <c r="Y37" t="n">
-        <v>214.9536679417165</v>
+        <v>408.7000000000879</v>
       </c>
     </row>
     <row r="38">
@@ -7177,13 +7177,13 @@
         <v>287.6254165811796</v>
       </c>
       <c r="N38" t="n">
-        <v>287.6254165811796</v>
+        <v>342.3384237357115</v>
       </c>
       <c r="O38" t="n">
-        <v>360.2405034917729</v>
+        <v>414.9535106463047</v>
       </c>
       <c r="P38" t="n">
-        <v>481.2869928454681</v>
+        <v>536</v>
       </c>
       <c r="Q38" t="n">
         <v>536</v>
@@ -7195,22 +7195,22 @@
         <v>483.0431684043335</v>
       </c>
       <c r="T38" t="n">
-        <v>483.0431684043335</v>
+        <v>347.6896330502783</v>
       </c>
       <c r="U38" t="n">
-        <v>347.6896330502752</v>
+        <v>321.6203271529333</v>
       </c>
       <c r="V38" t="n">
-        <v>262.0250615416213</v>
+        <v>186.2667917993685</v>
       </c>
       <c r="W38" t="n">
-        <v>262.0250615416213</v>
+        <v>186.2667917993685</v>
       </c>
       <c r="X38" t="n">
-        <v>126.6715261876771</v>
+        <v>186.2667917993685</v>
       </c>
       <c r="Y38" t="n">
-        <v>37.46199822524638</v>
+        <v>97.05726383693781</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>142.7674694370425</v>
+        <v>10.72</v>
       </c>
       <c r="C39" t="n">
-        <v>142.7674694370425</v>
+        <v>10.72</v>
       </c>
       <c r="D39" t="n">
-        <v>142.7674694370425</v>
+        <v>10.72</v>
       </c>
       <c r="E39" t="n">
-        <v>142.7674694370425</v>
+        <v>10.72</v>
       </c>
       <c r="F39" t="n">
-        <v>142.7674694370425</v>
+        <v>10.72</v>
       </c>
       <c r="G39" t="n">
-        <v>142.7674694370425</v>
+        <v>10.72</v>
       </c>
       <c r="H39" t="n">
         <v>10.72</v>
@@ -7244,13 +7244,13 @@
         <v>10.72</v>
       </c>
       <c r="J39" t="n">
-        <v>10.72</v>
+        <v>143.3800000000288</v>
       </c>
       <c r="K39" t="n">
         <v>143.3800000000288</v>
       </c>
       <c r="L39" t="n">
-        <v>143.3800000000288</v>
+        <v>276.0400000000577</v>
       </c>
       <c r="M39" t="n">
         <v>276.0400000000577</v>
@@ -7259,7 +7259,7 @@
         <v>403.3399999999712</v>
       </c>
       <c r="O39" t="n">
-        <v>403.3399999999712</v>
+        <v>536</v>
       </c>
       <c r="P39" t="n">
         <v>536</v>
@@ -7268,28 +7268,28 @@
         <v>419.9684191005256</v>
       </c>
       <c r="R39" t="n">
-        <v>323.037310724385</v>
+        <v>284.6148837469609</v>
       </c>
       <c r="S39" t="n">
-        <v>287.5888259116462</v>
+        <v>155.5413564746037</v>
       </c>
       <c r="T39" t="n">
-        <v>287.5888259116462</v>
+        <v>155.5413564746037</v>
       </c>
       <c r="U39" t="n">
-        <v>287.5888259116462</v>
+        <v>155.5413564746037</v>
       </c>
       <c r="V39" t="n">
-        <v>287.5888259116462</v>
+        <v>155.5413564746037</v>
       </c>
       <c r="W39" t="n">
-        <v>278.1210047906073</v>
+        <v>146.0735353535648</v>
       </c>
       <c r="X39" t="n">
-        <v>278.1210047906073</v>
+        <v>146.0735353535648</v>
       </c>
       <c r="Y39" t="n">
-        <v>278.1210047906073</v>
+        <v>146.0735353535648</v>
       </c>
     </row>
     <row r="40">
@@ -7299,52 +7299,52 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>347.6136679417463</v>
+        <v>10.72</v>
       </c>
       <c r="C40" t="n">
-        <v>347.6136679417463</v>
+        <v>10.72</v>
       </c>
       <c r="D40" t="n">
-        <v>347.6136679417463</v>
+        <v>10.72</v>
       </c>
       <c r="E40" t="n">
-        <v>347.6136679417463</v>
+        <v>10.72</v>
       </c>
       <c r="F40" t="n">
-        <v>347.6136679417463</v>
+        <v>10.72</v>
       </c>
       <c r="G40" t="n">
-        <v>347.6136679417463</v>
+        <v>143.3800000000288</v>
       </c>
       <c r="H40" t="n">
-        <v>347.6136679417463</v>
+        <v>276.0400000000577</v>
       </c>
       <c r="I40" t="n">
-        <v>347.6136679417463</v>
+        <v>408.7000000000866</v>
       </c>
       <c r="J40" t="n">
-        <v>347.6136679417463</v>
+        <v>536</v>
       </c>
       <c r="K40" t="n">
-        <v>480.2736679417751</v>
+        <v>536</v>
       </c>
       <c r="L40" t="n">
         <v>536</v>
       </c>
       <c r="M40" t="n">
-        <v>497.9140206067968</v>
+        <v>536</v>
       </c>
       <c r="N40" t="n">
-        <v>407.3246251510462</v>
+        <v>445.4106045442494</v>
       </c>
       <c r="O40" t="n">
-        <v>271.9710897969622</v>
+        <v>310.0570691901654</v>
       </c>
       <c r="P40" t="n">
-        <v>146.073535354073</v>
+        <v>174.7035338360845</v>
       </c>
       <c r="Q40" t="n">
-        <v>10.72</v>
+        <v>39.34999848201147</v>
       </c>
       <c r="R40" t="n">
         <v>10.72</v>
@@ -7353,22 +7353,22 @@
         <v>10.72</v>
       </c>
       <c r="T40" t="n">
-        <v>143.3800000000288</v>
+        <v>10.72</v>
       </c>
       <c r="U40" t="n">
-        <v>214.9536679417174</v>
+        <v>10.72</v>
       </c>
       <c r="V40" t="n">
-        <v>214.9536679417174</v>
+        <v>10.72</v>
       </c>
       <c r="W40" t="n">
-        <v>347.6136679417463</v>
+        <v>10.72</v>
       </c>
       <c r="X40" t="n">
-        <v>347.6136679417463</v>
+        <v>10.72</v>
       </c>
       <c r="Y40" t="n">
-        <v>347.6136679417463</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10.72</v>
+        <v>400.6464646464113</v>
       </c>
       <c r="C41" t="n">
-        <v>10.72</v>
+        <v>265.2929292928227</v>
       </c>
       <c r="D41" t="n">
-        <v>10.72</v>
+        <v>265.2929292928227</v>
       </c>
       <c r="E41" t="n">
-        <v>10.72</v>
+        <v>265.2929292928227</v>
       </c>
       <c r="F41" t="n">
-        <v>10.72</v>
+        <v>146.0735353542223</v>
       </c>
       <c r="G41" t="n">
-        <v>10.72</v>
+        <v>146.0735353542223</v>
       </c>
       <c r="H41" t="n">
         <v>10.72</v>
@@ -7429,25 +7429,25 @@
         <v>536</v>
       </c>
       <c r="S41" t="n">
-        <v>400.6464646457746</v>
+        <v>536</v>
       </c>
       <c r="T41" t="n">
-        <v>265.2929292915658</v>
+        <v>536</v>
       </c>
       <c r="U41" t="n">
-        <v>146.0735353540874</v>
+        <v>536</v>
       </c>
       <c r="V41" t="n">
-        <v>10.72</v>
+        <v>536</v>
       </c>
       <c r="W41" t="n">
-        <v>10.72</v>
+        <v>536</v>
       </c>
       <c r="X41" t="n">
-        <v>10.72</v>
+        <v>536</v>
       </c>
       <c r="Y41" t="n">
-        <v>10.72</v>
+        <v>536</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>265.2929292915624</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="C42" t="n">
-        <v>144.7704260266423</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="D42" t="n">
-        <v>144.7704260266423</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="E42" t="n">
-        <v>144.7704260266423</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="F42" t="n">
-        <v>144.7704260266423</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="G42" t="n">
-        <v>15.19109685994801</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="H42" t="n">
         <v>15.19109685994801</v>
@@ -7481,19 +7481,19 @@
         <v>10.72</v>
       </c>
       <c r="J42" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="K42" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="M42" t="n">
         <v>143.3800000000523</v>
       </c>
-      <c r="K42" t="n">
-        <v>143.3800000000523</v>
-      </c>
-      <c r="L42" t="n">
-        <v>270.6799999998955</v>
-      </c>
-      <c r="M42" t="n">
-        <v>403.3399999999477</v>
-      </c>
       <c r="N42" t="n">
-        <v>403.3399999999477</v>
+        <v>276.0400000001046</v>
       </c>
       <c r="O42" t="n">
         <v>403.3399999999477</v>
@@ -7505,28 +7505,28 @@
         <v>536</v>
       </c>
       <c r="R42" t="n">
-        <v>536</v>
+        <v>400.6464646457415</v>
       </c>
       <c r="S42" t="n">
-        <v>536</v>
+        <v>400.6464646457415</v>
       </c>
       <c r="T42" t="n">
-        <v>400.6464646457677</v>
+        <v>265.2929292915092</v>
       </c>
       <c r="U42" t="n">
-        <v>265.2929292915624</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="V42" t="n">
-        <v>265.2929292915624</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="W42" t="n">
-        <v>265.2929292915624</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="X42" t="n">
-        <v>265.2929292915624</v>
+        <v>147.2760334118886</v>
       </c>
       <c r="Y42" t="n">
-        <v>265.2929292915624</v>
+        <v>147.2760334118886</v>
       </c>
     </row>
     <row r="43">
@@ -7566,46 +7566,46 @@
         <v>174.924568116463</v>
       </c>
       <c r="L43" t="n">
-        <v>39.57103276220349</v>
+        <v>174.924568116463</v>
       </c>
       <c r="M43" t="n">
-        <v>39.57103276220349</v>
+        <v>174.924568116463</v>
       </c>
       <c r="N43" t="n">
-        <v>39.57103276220349</v>
+        <v>174.924568116463</v>
       </c>
       <c r="O43" t="n">
-        <v>39.57103276220349</v>
+        <v>39.57103276217106</v>
       </c>
       <c r="P43" t="n">
-        <v>39.57103276220349</v>
+        <v>37.14484950827628</v>
       </c>
       <c r="Q43" t="n">
-        <v>39.57103276220349</v>
+        <v>37.14484950827628</v>
       </c>
       <c r="R43" t="n">
-        <v>39.57103276220349</v>
+        <v>37.14484950827628</v>
       </c>
       <c r="S43" t="n">
-        <v>39.57103276220349</v>
+        <v>37.14484950827628</v>
       </c>
       <c r="T43" t="n">
-        <v>28.06484702148945</v>
+        <v>25.63866376756224</v>
       </c>
       <c r="U43" t="n">
-        <v>73.66668359420233</v>
+        <v>71.24050034027512</v>
       </c>
       <c r="V43" t="n">
-        <v>71.4744510525698</v>
+        <v>69.0482677986426</v>
       </c>
       <c r="W43" t="n">
-        <v>41.80494616498426</v>
+        <v>39.37876291105706</v>
       </c>
       <c r="X43" t="n">
-        <v>41.80494616498426</v>
+        <v>39.37876291105706</v>
       </c>
       <c r="Y43" t="n">
-        <v>41.80494616498426</v>
+        <v>39.37876291105706</v>
       </c>
     </row>
     <row r="44">
@@ -7615,16 +7615,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>536</v>
+        <v>10.72</v>
       </c>
       <c r="C44" t="n">
-        <v>416.7806060608542</v>
+        <v>10.72</v>
       </c>
       <c r="D44" t="n">
-        <v>281.4270707072361</v>
+        <v>10.72</v>
       </c>
       <c r="E44" t="n">
-        <v>146.0735353536181</v>
+        <v>10.72</v>
       </c>
       <c r="F44" t="n">
         <v>10.72</v>
@@ -7648,7 +7648,7 @@
         <v>287.6254165811796</v>
       </c>
       <c r="M44" t="n">
-        <v>342.3384237357115</v>
+        <v>287.6254165811796</v>
       </c>
       <c r="N44" t="n">
         <v>342.3384237357115</v>
@@ -7666,25 +7666,25 @@
         <v>536</v>
       </c>
       <c r="S44" t="n">
-        <v>536</v>
+        <v>416.7806060608542</v>
       </c>
       <c r="T44" t="n">
-        <v>536</v>
+        <v>416.7806060608542</v>
       </c>
       <c r="U44" t="n">
-        <v>536</v>
+        <v>281.4270707072361</v>
       </c>
       <c r="V44" t="n">
-        <v>536</v>
+        <v>146.0735353536181</v>
       </c>
       <c r="W44" t="n">
-        <v>536</v>
+        <v>10.72</v>
       </c>
       <c r="X44" t="n">
-        <v>536</v>
+        <v>10.72</v>
       </c>
       <c r="Y44" t="n">
-        <v>536</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="45">
@@ -7694,46 +7694,46 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>147.2760334118886</v>
+        <v>144.7704260266423</v>
       </c>
       <c r="C45" t="n">
-        <v>147.2760334118886</v>
+        <v>144.7704260266423</v>
       </c>
       <c r="D45" t="n">
-        <v>147.2760334118886</v>
+        <v>144.7704260266423</v>
       </c>
       <c r="E45" t="n">
-        <v>147.2760334118886</v>
+        <v>144.7704260266423</v>
       </c>
       <c r="F45" t="n">
-        <v>147.2760334118886</v>
+        <v>144.7704260266423</v>
       </c>
       <c r="G45" t="n">
-        <v>147.2760334118886</v>
+        <v>15.191096859948</v>
       </c>
       <c r="H45" t="n">
-        <v>15.19109685994801</v>
+        <v>15.191096859948</v>
       </c>
       <c r="I45" t="n">
         <v>10.72</v>
       </c>
       <c r="J45" t="n">
-        <v>143.3800000000811</v>
+        <v>10.72</v>
       </c>
       <c r="K45" t="n">
-        <v>143.3800000000811</v>
+        <v>10.72</v>
       </c>
       <c r="L45" t="n">
         <v>143.3800000000811</v>
       </c>
       <c r="M45" t="n">
-        <v>276.0400000001621</v>
+        <v>270.6799999998379</v>
       </c>
       <c r="N45" t="n">
         <v>403.339999999919</v>
       </c>
       <c r="O45" t="n">
-        <v>403.339999999919</v>
+        <v>536</v>
       </c>
       <c r="P45" t="n">
         <v>536</v>
@@ -7757,13 +7757,13 @@
         <v>400.6464646463819</v>
       </c>
       <c r="W45" t="n">
-        <v>265.2929292927638</v>
+        <v>400.6464646463819</v>
       </c>
       <c r="X45" t="n">
-        <v>147.2760334118886</v>
+        <v>280.1239613802603</v>
       </c>
       <c r="Y45" t="n">
-        <v>147.2760334118886</v>
+        <v>144.7704260266423</v>
       </c>
     </row>
     <row r="46">
@@ -7773,28 +7773,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>206.8279864068581</v>
+        <v>39.37876291105705</v>
       </c>
       <c r="C46" t="n">
-        <v>206.8279864068581</v>
+        <v>39.37876291105705</v>
       </c>
       <c r="D46" t="n">
-        <v>202.3724606935808</v>
+        <v>39.37876291105705</v>
       </c>
       <c r="E46" t="n">
-        <v>117.5432638885742</v>
+        <v>39.37876291105705</v>
       </c>
       <c r="F46" t="n">
-        <v>39.37876291105706</v>
+        <v>39.37876291105705</v>
       </c>
       <c r="G46" t="n">
-        <v>39.37876291105706</v>
+        <v>39.37876291105705</v>
       </c>
       <c r="H46" t="n">
         <v>10.72</v>
       </c>
       <c r="I46" t="n">
-        <v>42.26456811641078</v>
+        <v>42.26456811641077</v>
       </c>
       <c r="J46" t="n">
         <v>174.9245681164918</v>
@@ -7821,28 +7821,28 @@
         <v>174.9245681164918</v>
       </c>
       <c r="R46" t="n">
-        <v>174.9245681164918</v>
+        <v>172.4983848618944</v>
       </c>
       <c r="S46" t="n">
-        <v>174.9245681164918</v>
+        <v>37.14484950827629</v>
       </c>
       <c r="T46" t="n">
-        <v>163.4183823757778</v>
+        <v>25.63866376756224</v>
       </c>
       <c r="U46" t="n">
-        <v>209.0202189484907</v>
+        <v>71.24050034027512</v>
       </c>
       <c r="V46" t="n">
-        <v>206.8279864068581</v>
+        <v>69.0482677986426</v>
       </c>
       <c r="W46" t="n">
-        <v>206.8279864068581</v>
+        <v>39.37876291105705</v>
       </c>
       <c r="X46" t="n">
-        <v>206.8279864068581</v>
+        <v>39.37876291105705</v>
       </c>
       <c r="Y46" t="n">
-        <v>206.8279864068581</v>
+        <v>39.37876291105705</v>
       </c>
     </row>
   </sheetData>
@@ -7976,7 +7976,7 @@
         <v>394.6124995016138</v>
       </c>
       <c r="N2" t="n">
-        <v>380.4435062844021</v>
+        <v>325.1778424919457</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>80.78805116165627</v>
+        <v>136.0537149541127</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8046,22 +8046,22 @@
         <v>193.1741356901127</v>
       </c>
       <c r="K3" t="n">
-        <v>159.7282448080808</v>
+        <v>165.1423862222222</v>
       </c>
       <c r="L3" t="n">
-        <v>14.9879611111111</v>
+        <v>148.9879611111111</v>
       </c>
       <c r="M3" t="n">
-        <v>269.2047782656032</v>
+        <v>397.7906368514618</v>
       </c>
       <c r="N3" t="n">
-        <v>366.1839770626954</v>
+        <v>232.1839770626954</v>
       </c>
       <c r="O3" t="n">
         <v>32.73077689815733</v>
       </c>
       <c r="P3" t="n">
-        <v>152.4087073258962</v>
+        <v>18.40870732589624</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>55.26566379245638</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8210,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>394.6124995016138</v>
+        <v>449.8781632940702</v>
       </c>
       <c r="N5" t="n">
         <v>325.1778424919457</v>
@@ -8289,13 +8289,13 @@
         <v>14.9879611111111</v>
       </c>
       <c r="M6" t="n">
-        <v>397.7906368514618</v>
+        <v>403.2047782656032</v>
       </c>
       <c r="N6" t="n">
         <v>366.1839770626954</v>
       </c>
       <c r="O6" t="n">
-        <v>166.7307768981573</v>
+        <v>161.316635484016</v>
       </c>
       <c r="P6" t="n">
         <v>152.4087073258962</v>
@@ -8523,16 +8523,16 @@
         <v>222.1423862222222</v>
       </c>
       <c r="L9" t="n">
-        <v>29.98018315626357</v>
+        <v>14.9879611111111</v>
       </c>
       <c r="M9" t="n">
-        <v>460.2047782656032</v>
+        <v>284.1970003107556</v>
       </c>
       <c r="N9" t="n">
         <v>423.1839770626954</v>
       </c>
       <c r="O9" t="n">
-        <v>32.73077689815733</v>
+        <v>223.7307768981573</v>
       </c>
       <c r="P9" t="n">
         <v>18.40870732589624</v>
@@ -8678,16 +8678,16 @@
         <v>290.7083931797637</v>
       </c>
       <c r="K11" t="n">
-        <v>219.5891658291458</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>193.5067738693467</v>
       </c>
       <c r="M11" t="n">
-        <v>394.6124995016138</v>
+        <v>722.6124995016138</v>
       </c>
       <c r="N11" t="n">
-        <v>444.3075634371088</v>
+        <v>335.8967292662546</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8754,13 +8754,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J12" t="n">
-        <v>59.17413569011271</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K12" t="n">
-        <v>31.1423862222222</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L12" t="n">
-        <v>329.2788390707735</v>
+        <v>14.9879611111111</v>
       </c>
       <c r="M12" t="n">
         <v>471.6948204301074</v>
@@ -8769,7 +8769,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O12" t="n">
-        <v>360.7307768981573</v>
+        <v>241.9931939793527</v>
       </c>
       <c r="P12" t="n">
         <v>219.1507118405495</v>
@@ -8912,16 +8912,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>290.7083931797637</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>166.9340538234193</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>394.6124995016138</v>
+        <v>722.6124995016138</v>
       </c>
       <c r="N14" t="n">
         <v>653.1778424919457</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>285.013711805312</v>
+        <v>80.78805116165627</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -8991,13 +8991,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J15" t="n">
-        <v>59.17413569011271</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K15" t="n">
-        <v>218.1752686965378</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L15" t="n">
-        <v>342.9879611111111</v>
+        <v>14.9879611111111</v>
       </c>
       <c r="M15" t="n">
         <v>471.6948204301074</v>
@@ -9006,10 +9006,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O15" t="n">
-        <v>360.7307768981573</v>
+        <v>241.9931939793527</v>
       </c>
       <c r="P15" t="n">
-        <v>18.40870732589624</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q15" t="n">
         <v>17.27519534353338</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>290.7083931797637</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -9158,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>722.6124995016138</v>
+        <v>598.8381601452694</v>
       </c>
       <c r="N17" t="n">
-        <v>492.1118963153651</v>
+        <v>325.1778424919457</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9228,13 +9228,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J18" t="n">
-        <v>59.17413569011271</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K18" t="n">
-        <v>218.1752686965378</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L18" t="n">
-        <v>342.9879611111111</v>
+        <v>14.9879611111111</v>
       </c>
       <c r="M18" t="n">
         <v>471.6948204301074</v>
@@ -9243,10 +9243,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>360.7307768981573</v>
+        <v>241.9931939793527</v>
       </c>
       <c r="P18" t="n">
-        <v>18.40870732589624</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q18" t="n">
         <v>17.27519534353338</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>290.7083931797637</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>71.84341444596721</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>394.6124995016138</v>
+        <v>561.5465533250332</v>
       </c>
       <c r="N20" t="n">
-        <v>325.1778424919457</v>
+        <v>653.1778424919457</v>
       </c>
       <c r="O20" t="n">
-        <v>254.6514273630371</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>205.7308188346512</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>80.78805116165627</v>
+        <v>408.7880511616563</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9465,7 +9465,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J21" t="n">
-        <v>59.17413569011271</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K21" t="n">
         <v>295.8802408630135</v>
@@ -9477,7 +9477,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N21" t="n">
-        <v>407.7035550048745</v>
+        <v>239.4129487671988</v>
       </c>
       <c r="O21" t="n">
         <v>360.7307768981573</v>
@@ -9623,28 +9623,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>367.7083931797789</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>270.5067738693467</v>
       </c>
       <c r="M23" t="n">
-        <v>712.4354422138916</v>
+        <v>601.48945633013</v>
       </c>
       <c r="N23" t="n">
-        <v>730.177842491961</v>
+        <v>325.1778424919457</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>282.7308188346665</v>
       </c>
       <c r="Q23" t="n">
-        <v>485.7880511616715</v>
+        <v>80.78805116165627</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9714,10 +9714,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N24" t="n">
-        <v>485.4085271713503</v>
+        <v>276.5074358900012</v>
       </c>
       <c r="O24" t="n">
-        <v>173.7807075195547</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P24" t="n">
         <v>219.1507118405495</v>
@@ -9869,19 +9869,19 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>394.6124995016138</v>
+        <v>722.6124995016353</v>
       </c>
       <c r="N26" t="n">
-        <v>653.1778424919671</v>
+        <v>492.1118963153223</v>
       </c>
       <c r="O26" t="n">
-        <v>254.6514273630586</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>321.0706776219956</v>
+        <v>408.7880511616777</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9942,19 +9942,19 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K27" t="n">
-        <v>31.1423862222222</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L27" t="n">
-        <v>342.9879611111326</v>
+        <v>14.9879611111111</v>
       </c>
       <c r="M27" t="n">
-        <v>471.6948204301074</v>
+        <v>352.9572375112815</v>
       </c>
       <c r="N27" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O27" t="n">
-        <v>178.7310486201226</v>
+        <v>360.7307768981788</v>
       </c>
       <c r="P27" t="n">
         <v>219.1507118405495</v>
@@ -10100,13 +10100,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>166.9340538233765</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>561.5465533249903</v>
+        <v>722.6124995016353</v>
       </c>
       <c r="N29" t="n">
         <v>653.1778424919671</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>408.7880511616777</v>
+        <v>80.78805116165627</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10179,10 +10179,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K30" t="n">
-        <v>31.1423862222222</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L30" t="n">
-        <v>342.9879611111326</v>
+        <v>14.9879611111111</v>
       </c>
       <c r="M30" t="n">
         <v>471.6948204301074</v>
@@ -10191,10 +10191,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O30" t="n">
-        <v>360.7307768981788</v>
+        <v>241.9931939793527</v>
       </c>
       <c r="P30" t="n">
-        <v>37.15098356249331</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q30" t="n">
         <v>17.27519534353338</v>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>449.8495836280222</v>
+        <v>665.6124995016344</v>
       </c>
       <c r="N32" t="n">
         <v>596.1778424919662</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>351.7880511616768</v>
+        <v>136.0251352880648</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10413,25 +10413,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
-        <v>59.17413569011271</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K33" t="n">
-        <v>106.4782989995271</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L33" t="n">
-        <v>285.9879611111317</v>
+        <v>14.9879611111111</v>
       </c>
       <c r="M33" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N33" t="n">
-        <v>485.4085271713503</v>
+        <v>468.9739745555761</v>
       </c>
       <c r="O33" t="n">
-        <v>303.7307768981779</v>
+        <v>32.73077689815733</v>
       </c>
       <c r="P33" t="n">
-        <v>18.40870732589624</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10583,7 +10583,7 @@
         <v>394.6124995016138</v>
       </c>
       <c r="N35" t="n">
-        <v>380.4435062844021</v>
+        <v>325.1778424919457</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>80.78805116165627</v>
+        <v>136.0537149541127</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10650,25 +10650,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>59.17413569011271</v>
+        <v>187.7599942758825</v>
       </c>
       <c r="K36" t="n">
-        <v>165.1423862222518</v>
+        <v>31.1423862222222</v>
       </c>
       <c r="L36" t="n">
-        <v>14.9879611111111</v>
+        <v>148.9879611111407</v>
       </c>
       <c r="M36" t="n">
         <v>403.2047782656327</v>
       </c>
       <c r="N36" t="n">
-        <v>360.7698356484652</v>
+        <v>232.1839770626954</v>
       </c>
       <c r="O36" t="n">
-        <v>32.73077689815733</v>
+        <v>166.7307768981869</v>
       </c>
       <c r="P36" t="n">
-        <v>152.4087073259258</v>
+        <v>18.40870732589624</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10820,7 +10820,7 @@
         <v>394.6124995016138</v>
       </c>
       <c r="N38" t="n">
-        <v>325.1778424919457</v>
+        <v>380.4435062844021</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>136.0537149541127</v>
+        <v>80.78805116165627</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10887,25 +10887,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>59.17413569011271</v>
+        <v>193.1741356901418</v>
       </c>
       <c r="K39" t="n">
-        <v>165.1423862222513</v>
+        <v>31.1423862222222</v>
       </c>
       <c r="L39" t="n">
-        <v>14.9879611111111</v>
+        <v>148.9879611111402</v>
       </c>
       <c r="M39" t="n">
-        <v>403.2047782656323</v>
+        <v>269.2047782656032</v>
       </c>
       <c r="N39" t="n">
         <v>360.7698356484665</v>
       </c>
       <c r="O39" t="n">
-        <v>32.73077689815733</v>
+        <v>166.7307768981865</v>
       </c>
       <c r="P39" t="n">
-        <v>152.4087073259254</v>
+        <v>18.40870732589624</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11124,22 +11124,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>193.1741356901655</v>
+        <v>59.17413569011271</v>
       </c>
       <c r="K42" t="n">
         <v>31.1423862222222</v>
       </c>
       <c r="L42" t="n">
-        <v>143.5738196968113</v>
+        <v>14.9879611111111</v>
       </c>
       <c r="M42" t="n">
         <v>403.2047782656559</v>
       </c>
       <c r="N42" t="n">
-        <v>232.1839770626954</v>
+        <v>366.1839770627482</v>
       </c>
       <c r="O42" t="n">
-        <v>32.73077689815733</v>
+        <v>161.3166354838575</v>
       </c>
       <c r="P42" t="n">
         <v>152.408707325949</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>449.8781632940702</v>
+        <v>394.6124995016138</v>
       </c>
       <c r="N44" t="n">
-        <v>325.1778424919457</v>
+        <v>380.4435062844021</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11361,25 +11361,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>193.1741356901946</v>
+        <v>59.17413569011271</v>
       </c>
       <c r="K45" t="n">
         <v>31.1423862222222</v>
       </c>
       <c r="L45" t="n">
-        <v>14.9879611111111</v>
+        <v>148.987961111193</v>
       </c>
       <c r="M45" t="n">
-        <v>403.204778265685</v>
+        <v>397.7906368512163</v>
       </c>
       <c r="N45" t="n">
-        <v>360.7698356483085</v>
+        <v>366.1839770627773</v>
       </c>
       <c r="O45" t="n">
-        <v>32.73077689815733</v>
+        <v>166.7307768982392</v>
       </c>
       <c r="P45" t="n">
-        <v>152.4087073259781</v>
+        <v>18.40870732589624</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22512,16 +22512,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
@@ -22566,19 +22566,19 @@
         <v>75.42726327970985</v>
       </c>
       <c r="T2" t="n">
-        <v>176.2350405420235</v>
+        <v>182.9448078592171</v>
       </c>
       <c r="U2" t="n">
         <v>249.1531156440881</v>
       </c>
       <c r="V2" t="n">
-        <v>95.85102416682389</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
         <v>104.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>58.28183346066771</v>
+        <v>63.74840268876096</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>60.7051195992712</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22712,10 +22712,10 @@
         <v>52.40989194786738</v>
       </c>
       <c r="P4" t="n">
-        <v>241.2110448692611</v>
+        <v>107.2110448692611</v>
       </c>
       <c r="Q4" t="n">
-        <v>215.1886875260624</v>
+        <v>288.4835679267911</v>
       </c>
       <c r="R4" t="n">
         <v>175.4127509319708</v>
@@ -22758,10 +22758,10 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>75.42726327970983</v>
       </c>
       <c r="T5" t="n">
-        <v>67.82271883970077</v>
+        <v>182.9448078592171</v>
       </c>
       <c r="U5" t="n">
         <v>115.1531156440881</v>
@@ -22815,7 +22815,7 @@
         <v>104.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>86.41266275603174</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -22940,10 +22940,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>60.70511959927121</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>112.6835015011931</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>52.4098919478674</v>
@@ -22952,10 +22952,10 @@
         <v>107.2110448692611</v>
       </c>
       <c r="Q7" t="n">
-        <v>159.827266425598</v>
+        <v>215.1886875260623</v>
       </c>
       <c r="R7" t="n">
-        <v>191.3855509319707</v>
+        <v>309.4127509319707</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22992,13 +22992,13 @@
         <v>46.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7.339155739849787</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.889628708011855</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -23037,22 +23037,22 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>72.42726327970985</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>55.15311564408805</v>
+        <v>66.86512350334979</v>
       </c>
       <c r="V8" t="n">
-        <v>226.8510241668239</v>
+        <v>35.85102416680161</v>
       </c>
       <c r="W8" t="n">
-        <v>137.3866546352725</v>
+        <v>44.37347598092526</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>189.2818334606677</v>
       </c>
       <c r="Y8" t="n">
         <v>108.3174326828064</v>
@@ -23177,22 +23177,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>57.70511959927121</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>109.6835015011931</v>
       </c>
       <c r="O10" t="n">
-        <v>15.17709194786746</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>47.21104486926109</v>
+        <v>47.21104486926112</v>
       </c>
       <c r="Q10" t="n">
         <v>99.827266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>115.4127509319707</v>
+        <v>188.2949624791095</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23223,19 +23223,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>174.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>142.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>103.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>97.88962870801186</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -23286,13 +23286,13 @@
         <v>322.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>3.373475980947546</v>
+        <v>331.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>153.5455572436648</v>
+        <v>100.1510718525971</v>
       </c>
       <c r="Y11" t="n">
-        <v>204.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23414,7 +23414,7 @@
         <v>59.71077569876277</v>
       </c>
       <c r="M13" t="n">
-        <v>153.7051195992712</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>6.211044869261094</v>
       </c>
       <c r="Q13" t="n">
-        <v>303.7293789217763</v>
+        <v>129.4344985210476</v>
       </c>
       <c r="R13" t="n">
-        <v>74.41275093197073</v>
+        <v>402.4127509319707</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -23469,7 +23469,7 @@
         <v>103.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F14" t="n">
         <v>97.88962870801186</v>
@@ -23478,7 +23478,7 @@
         <v>95.90511098048353</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>92.2814375979998</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,25 +23511,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>168.4272632797098</v>
       </c>
       <c r="T14" t="n">
-        <v>173.5646886540937</v>
+        <v>275.9448078592171</v>
       </c>
       <c r="U14" t="n">
-        <v>342.1531156440881</v>
+        <v>14.15311564400656</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>331.3734759809475</v>
+        <v>3.373475980880016</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>195.5478903104471</v>
       </c>
     </row>
     <row r="15">
@@ -23648,28 +23648,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>59.71077569876275</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>205.6835015011931</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>334.2110448692611</v>
+        <v>6.211044869261116</v>
       </c>
       <c r="Q16" t="n">
         <v>58.827266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>96.30886398030265</v>
+        <v>327.04725722499</v>
       </c>
       <c r="S16" t="n">
-        <v>48.71111904711773</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23697,22 +23697,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93.99931295557451</v>
+        <v>17.68226856224732</v>
       </c>
       <c r="C17" t="n">
-        <v>61.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>16.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>16.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>14.90511098048353</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>11.2814375979998</v>
@@ -23748,10 +23748,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>87.42726327970985</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>194.9448078592171</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>90.44655307426075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23888,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.347175275161533</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23897,7 +23897,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.347175275161504</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -23934,25 +23934,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32.5772354571132</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>61.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>22.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>16.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>16.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>14.90511098048353</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>11.2814375979998</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23985,13 +23985,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>87.42726327970985</v>
       </c>
       <c r="T20" t="n">
-        <v>194.9448078592171</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>73.87819365703137</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -24003,7 +24003,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>123.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -24131,10 +24131,10 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.347175275161504</v>
       </c>
       <c r="P22" t="n">
-        <v>3.347175275161504</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -24222,13 +24222,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>70.87746690604283</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>70.87746690604268</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -24411,22 +24411,22 @@
         <v>174.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>142.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>103.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>97.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>95.90511098048354</v>
       </c>
       <c r="H26" t="n">
-        <v>92.28143759799977</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,16 +24459,16 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>109.8550512188505</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>14.15311564406657</v>
+        <v>14.15311564386877</v>
       </c>
       <c r="V26" t="n">
-        <v>68.13442928861622</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>331.3734759809475</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>59.71077569876277</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24608,10 +24608,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>6.211044869239664</v>
+        <v>6.211044869030502</v>
       </c>
       <c r="Q28" t="n">
-        <v>189.1452742198318</v>
+        <v>129.4344985212782</v>
       </c>
       <c r="R28" t="n">
         <v>402.4127509319707</v>
@@ -24654,7 +24654,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>63.66754651479113</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>92.28143759799977</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,7 +24699,7 @@
         <v>168.4272632797098</v>
       </c>
       <c r="T29" t="n">
-        <v>275.9448078592171</v>
+        <v>275.9448078592172</v>
       </c>
       <c r="U29" t="n">
         <v>342.1531156440881</v>
@@ -24708,10 +24708,10 @@
         <v>322.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>3.373475980744956</v>
+        <v>260.0414183582039</v>
       </c>
       <c r="X29" t="n">
-        <v>285.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>279.4098919478674</v>
       </c>
       <c r="P31" t="n">
-        <v>185.11916071614</v>
+        <v>185.1191607161401</v>
       </c>
       <c r="Q31" t="n">
         <v>58.82726642533623</v>
@@ -24885,7 +24885,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>26.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>152.1260442728291</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -24948,7 +24948,7 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>125.6514660298351</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -25088,7 +25088,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>15.41275093156696</v>
+        <v>15.41275093197072</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25176,16 +25176,16 @@
         <v>159.9448078592171</v>
       </c>
       <c r="U35" t="n">
-        <v>147.9172395255221</v>
+        <v>226.1531156440881</v>
       </c>
       <c r="V35" t="n">
         <v>72.85102416679433</v>
       </c>
       <c r="W35" t="n">
-        <v>81.37347598091793</v>
+        <v>137.1375998623815</v>
       </c>
       <c r="X35" t="n">
-        <v>169.2818334606677</v>
+        <v>35.2818334606381</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -25310,22 +25310,22 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>37.7051195992712</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>29.40989194783782</v>
+        <v>135.0661934491493</v>
       </c>
       <c r="P37" t="n">
         <v>84.21104486923156</v>
       </c>
       <c r="Q37" t="n">
-        <v>146.1886875261214</v>
+        <v>136.8272664255685</v>
       </c>
       <c r="R37" t="n">
-        <v>286.4127509319708</v>
+        <v>152.4127509319411</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>58.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25410,19 +25410,19 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>159.9448078592171</v>
+        <v>25.94480785870246</v>
       </c>
       <c r="U38" t="n">
-        <v>92.15311564357046</v>
+        <v>200.3445028057165</v>
       </c>
       <c r="V38" t="n">
-        <v>122.0430983732565</v>
+        <v>72.85102416679479</v>
       </c>
       <c r="W38" t="n">
         <v>215.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>35.28183346026299</v>
+        <v>169.2818334606677</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -25547,7 +25547,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>37.70511959927121</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -25556,13 +25556,13 @@
         <v>29.40989194732424</v>
       </c>
       <c r="P40" t="n">
-        <v>93.57246597080078</v>
+        <v>84.21104486872105</v>
       </c>
       <c r="Q40" t="n">
         <v>136.8272664250657</v>
       </c>
       <c r="R40" t="n">
-        <v>286.4127509319708</v>
+        <v>258.0690524347793</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25593,10 +25593,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>284.9993129555745</v>
+        <v>150.9993129555218</v>
       </c>
       <c r="C41" t="n">
-        <v>252.4745782429939</v>
+        <v>118.4745782429411</v>
       </c>
       <c r="D41" t="n">
         <v>213.3391557398498</v>
@@ -25605,13 +25605,13 @@
         <v>207.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>207.8896287080119</v>
+        <v>89.86242870879751</v>
       </c>
       <c r="G41" t="n">
         <v>205.9051109804836</v>
       </c>
       <c r="H41" t="n">
-        <v>202.2814375979998</v>
+        <v>68.28143759731967</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,19 +25641,19 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.3427395317662558</v>
+        <v>0.3427395318120148</v>
       </c>
       <c r="S41" t="n">
-        <v>144.4272632790267</v>
+        <v>278.4272632797098</v>
       </c>
       <c r="T41" t="n">
-        <v>251.9448078585504</v>
+        <v>385.9448078592172</v>
       </c>
       <c r="U41" t="n">
-        <v>334.1259156459845</v>
+        <v>452.1531156440881</v>
       </c>
       <c r="V41" t="n">
-        <v>298.8510241662773</v>
+        <v>432.8510241668239</v>
       </c>
       <c r="W41" t="n">
         <v>441.3734759809475</v>
@@ -25675,7 +25675,7 @@
         <v>187.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>44.78263421324837</v>
+        <v>164.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>150.9376868977026</v>
@@ -25687,10 +25687,10 @@
         <v>142.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>128.2835358750274</v>
       </c>
       <c r="H42" t="n">
-        <v>130.7640871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>321.9617972923793</v>
+        <v>187.9617972916633</v>
       </c>
       <c r="S42" t="n">
         <v>261.0939999646113</v>
@@ -25729,7 +25729,7 @@
         <v>72.51976521682383</v>
       </c>
       <c r="U42" t="n">
-        <v>69.18035975952358</v>
+        <v>86.34363283936236</v>
       </c>
       <c r="V42" t="n">
         <v>217.5106671915202</v>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>87.71187891569073</v>
+        <v>90.11380033707866</v>
       </c>
       <c r="C43" t="n">
         <v>75.72524664804467</v>
@@ -25781,7 +25781,7 @@
         <v>47.10503609622502</v>
       </c>
       <c r="L43" t="n">
-        <v>35.71077569804584</v>
+        <v>169.7107756987628</v>
       </c>
       <c r="M43" t="n">
         <v>263.7051195992712</v>
@@ -25790,10 +25790,10 @@
         <v>315.6835015011931</v>
       </c>
       <c r="O43" t="n">
-        <v>389.4098919478674</v>
+        <v>255.4098919471184</v>
       </c>
       <c r="P43" t="n">
-        <v>444.2110448692611</v>
+        <v>441.8091234479053</v>
       </c>
       <c r="Q43" t="n">
         <v>496.827266425598</v>
@@ -25833,19 +25833,19 @@
         <v>284.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>134.4473782432396</v>
+        <v>252.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>79.33915573976788</v>
+        <v>213.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>73.36328960678679</v>
+        <v>207.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>73.88962870793</v>
+        <v>207.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>205.9051109804836</v>
+        <v>205.9051109804835</v>
       </c>
       <c r="H44" t="n">
         <v>202.2814375979998</v>
@@ -25881,19 +25881,19 @@
         <v>0.3427395318120148</v>
       </c>
       <c r="S44" t="n">
-        <v>278.4272632797098</v>
+        <v>160.4000632799555</v>
       </c>
       <c r="T44" t="n">
-        <v>385.9448078592172</v>
+        <v>385.9448078592171</v>
       </c>
       <c r="U44" t="n">
-        <v>452.1531156440881</v>
+        <v>318.1531156440062</v>
       </c>
       <c r="V44" t="n">
-        <v>432.8510241668239</v>
+        <v>298.851024166742</v>
       </c>
       <c r="W44" t="n">
-        <v>441.3734759809475</v>
+        <v>307.3734759808656</v>
       </c>
       <c r="X44" t="n">
         <v>395.2818334606677</v>
@@ -25924,10 +25924,10 @@
         <v>142.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>128.2835358750274</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>130.7640871864211</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25966,19 +25966,19 @@
         <v>206.5197652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>203.1803597601867</v>
+        <v>203.1803597601868</v>
       </c>
       <c r="V45" t="n">
         <v>83.5106671914383</v>
       </c>
       <c r="W45" t="n">
-        <v>101.3731429097467</v>
+        <v>235.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>106.0260125233211</v>
+        <v>103.5454612119272</v>
       </c>
       <c r="Y45" t="n">
-        <v>202.3913927661343</v>
+        <v>68.39139276605249</v>
       </c>
     </row>
     <row r="46">
@@ -25994,13 +25994,13 @@
         <v>75.72524664804467</v>
       </c>
       <c r="D46" t="n">
-        <v>84.12524759941087</v>
+        <v>88.53621805555548</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>83.98090483695654</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>77.38285596774193</v>
       </c>
       <c r="G46" t="n">
         <v>47.66157775956282</v>
@@ -26015,10 +26015,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>47.10503609622502</v>
+        <v>47.10503609622504</v>
       </c>
       <c r="L46" t="n">
-        <v>169.7107756987628</v>
+        <v>169.7107756987627</v>
       </c>
       <c r="M46" t="n">
         <v>263.7051195992712</v>
@@ -26033,13 +26033,13 @@
         <v>444.2110448692611</v>
       </c>
       <c r="Q46" t="n">
-        <v>496.827266425598</v>
+        <v>496.8272664255981</v>
       </c>
       <c r="R46" t="n">
-        <v>512.4127509319708</v>
+        <v>510.0108295099193</v>
       </c>
       <c r="S46" t="n">
-        <v>158.7111190471177</v>
+        <v>24.71111904703582</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26051,7 +26051,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>29.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>50.44364543010755</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3845434.654408468</v>
+        <v>3845434.654408467</v>
       </c>
     </row>
     <row r="6">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8627448.728504574</v>
+        <v>8627448.728504576</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9530392.198045665</v>
+        <v>9530392.198045667</v>
       </c>
     </row>
     <row r="12">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12392696.2256943</v>
+        <v>12392696.22569429</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13016797.75831393</v>
+        <v>13016797.75831392</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13640899.29093357</v>
+        <v>13640899.29093356</v>
       </c>
     </row>
   </sheetData>
@@ -26275,22 +26275,22 @@
         <v>1111744.714407417</v>
       </c>
       <c r="D2" t="n">
-        <v>1136868.174051762</v>
+        <v>1136868.174051761</v>
       </c>
       <c r="E2" t="n">
-        <v>1072245.370080051</v>
+        <v>1072245.37008005</v>
       </c>
       <c r="F2" t="n">
         <v>1072245.37008005</v>
       </c>
       <c r="G2" t="n">
+        <v>1171551.269280258</v>
+      </c>
+      <c r="H2" t="n">
         <v>1171551.269280257</v>
       </c>
-      <c r="H2" t="n">
-        <v>1171551.269280258</v>
-      </c>
       <c r="I2" t="n">
-        <v>1191048.43426853</v>
+        <v>1191048.434268529</v>
       </c>
       <c r="J2" t="n">
         <v>1072245.37008005</v>
@@ -26299,19 +26299,19 @@
         <v>1072245.37008005</v>
       </c>
       <c r="L2" t="n">
-        <v>1184553.006126815</v>
+        <v>1184553.006126805</v>
       </c>
       <c r="M2" t="n">
         <v>1132245.69153978</v>
       </c>
       <c r="N2" t="n">
-        <v>1132245.69153978</v>
+        <v>1132245.691539781</v>
       </c>
       <c r="O2" t="n">
-        <v>741120.5699858</v>
+        <v>741120.5699857965</v>
       </c>
       <c r="P2" t="n">
-        <v>741120.5699857969</v>
+        <v>741120.5699857965</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>579717.3968009809</v>
+        <v>579710.1723028626</v>
       </c>
       <c r="C4" t="n">
-        <v>577682.6450101846</v>
+        <v>577675.4205120663</v>
       </c>
       <c r="D4" t="n">
-        <v>588120.2074786475</v>
+        <v>588111.716158919</v>
       </c>
       <c r="E4" t="n">
-        <v>541628.8869774824</v>
+        <v>541617.3464932523</v>
       </c>
       <c r="F4" t="n">
-        <v>539892.8048843762</v>
+        <v>539881.2644001463</v>
       </c>
       <c r="G4" t="n">
-        <v>596840.1022959088</v>
+        <v>596828.5618116788</v>
       </c>
       <c r="H4" t="n">
-        <v>594857.3597171477</v>
+        <v>594845.8192329176</v>
       </c>
       <c r="I4" t="n">
-        <v>601205.8987033223</v>
+        <v>601192.6444551024</v>
       </c>
       <c r="J4" t="n">
-        <v>532924.3463083707</v>
+        <v>532912.8058241408</v>
       </c>
       <c r="K4" t="n">
-        <v>531176.1115161437</v>
+        <v>531164.5710319137</v>
       </c>
       <c r="L4" t="n">
-        <v>596461.9373793971</v>
+        <v>596451.6655256477</v>
       </c>
       <c r="M4" t="n">
-        <v>568994.6400333323</v>
+        <v>568987.415535214</v>
       </c>
       <c r="N4" t="n">
-        <v>566878.0580220579</v>
+        <v>566870.8335239396</v>
       </c>
       <c r="O4" t="n">
-        <v>341183.4061841136</v>
+        <v>341176.1816859932</v>
       </c>
       <c r="P4" t="n">
-        <v>340024.504754268</v>
+        <v>340017.2802561497</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>231762.9176064363</v>
+        <v>231770.1421045546</v>
       </c>
       <c r="C6" t="n">
-        <v>487665.6693972324</v>
+        <v>487672.8938953504</v>
       </c>
       <c r="D6" t="n">
-        <v>476169.7595731142</v>
+        <v>476178.2508928424</v>
       </c>
       <c r="E6" t="n">
-        <v>188819.3001025682</v>
+        <v>188830.8405867977</v>
       </c>
       <c r="F6" t="n">
-        <v>481979.3821956736</v>
+        <v>481990.9226799033</v>
       </c>
       <c r="G6" t="n">
-        <v>452728.3949843483</v>
+        <v>452739.9354685788</v>
       </c>
       <c r="H6" t="n">
-        <v>519511.13756311</v>
+        <v>519522.6780473398</v>
       </c>
       <c r="I6" t="n">
-        <v>501126.3705652077</v>
+        <v>501139.6248134267</v>
       </c>
       <c r="J6" t="n">
-        <v>288083.8407716794</v>
+        <v>288095.3812559093</v>
       </c>
       <c r="K6" t="n">
-        <v>490696.0755639062</v>
+        <v>490707.6160481363</v>
       </c>
       <c r="L6" t="n">
-        <v>373831.4817474177</v>
+        <v>373841.7536011575</v>
       </c>
       <c r="M6" t="n">
-        <v>514921.0645064482</v>
+        <v>514928.2890045665</v>
       </c>
       <c r="N6" t="n">
-        <v>517037.6465177224</v>
+        <v>517044.8710158411</v>
       </c>
       <c r="O6" t="n">
-        <v>370606.7708016864</v>
+        <v>370613.9952998033</v>
       </c>
       <c r="P6" t="n">
-        <v>371765.672231529</v>
+        <v>371772.8967296468</v>
       </c>
     </row>
   </sheetData>
@@ -27512,13 +27512,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>250.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>227.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>213.9376868977026</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27533,7 +27533,7 @@
         <v>327.7640871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>177.7729227632556</v>
+        <v>201.4263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>110.3465368719069</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27597,31 +27597,31 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.6615777595628</v>
+        <v>378.6615777595629</v>
       </c>
       <c r="H4" t="n">
         <v>359.3721752819465</v>
       </c>
       <c r="I4" t="n">
-        <v>299.1367998824134</v>
+        <v>216.1445532141525</v>
       </c>
       <c r="J4" t="n">
         <v>8.240686540825806</v>
       </c>
       <c r="K4" t="n">
-        <v>244.105036096225</v>
+        <v>378.105036096225</v>
       </c>
       <c r="L4" t="n">
-        <v>366.7107756987627</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>355.7111190471177</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>208.3911238833069</v>
@@ -27657,7 +27657,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>269.9485780392636</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27758,7 +27758,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>319.0186340938196</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27794,22 +27794,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>114.8712650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>384.9617972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>324.0939999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>269.5197652175138</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>348.8997093069229</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>265.3913927661343</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27846,16 +27846,16 @@
         <v>244.6615777595628</v>
       </c>
       <c r="H7" t="n">
-        <v>229.5687884268218</v>
+        <v>225.3721752819465</v>
       </c>
       <c r="I7" t="n">
-        <v>299.1367998824134</v>
+        <v>165.1367998824134</v>
       </c>
       <c r="J7" t="n">
-        <v>8.240686540825806</v>
+        <v>12.43729968570111</v>
       </c>
       <c r="K7" t="n">
-        <v>244.105036096225</v>
+        <v>378.105036096225</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27986,19 +27986,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>193.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>156.9376868977026</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>151.6720972219126</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>148.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.2835358750273</v>
@@ -28007,7 +28007,7 @@
         <v>327.7640871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>186.3869630030688</v>
+        <v>201.4263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>114.8712650904796</v>
       </c>
       <c r="R9" t="n">
         <v>403</v>
@@ -28052,7 +28052,7 @@
         <v>403</v>
       </c>
       <c r="X9" t="n">
-        <v>403</v>
+        <v>273.0893120212407</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>403</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>403</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>403</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>403</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>403</v>
       </c>
       <c r="G10" t="n">
-        <v>244.6615777595628</v>
+        <v>403</v>
       </c>
       <c r="H10" t="n">
-        <v>225.3721752819465</v>
+        <v>403</v>
       </c>
       <c r="I10" t="n">
-        <v>165.1367998824134</v>
+        <v>356.1367998824134</v>
       </c>
       <c r="J10" t="n">
-        <v>8.240686540825806</v>
+        <v>72.65089953166807</v>
       </c>
       <c r="K10" t="n">
         <v>244.105036096225</v>
       </c>
       <c r="L10" t="n">
-        <v>366.7107756987627</v>
+        <v>403</v>
       </c>
       <c r="M10" t="n">
         <v>403</v>
@@ -28119,7 +28119,7 @@
         <v>355.7111190471177</v>
       </c>
       <c r="T10" t="n">
-        <v>234.8783308609748</v>
+        <v>208.3911238833069</v>
       </c>
       <c r="U10" t="n">
         <v>150.9375388154415</v>
@@ -28134,7 +28134,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>403</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28302,7 +28302,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>307</v>
+        <v>301.7835571870699</v>
       </c>
       <c r="C13" t="n">
         <v>307</v>
@@ -28329,7 +28329,7 @@
         <v>307</v>
       </c>
       <c r="K13" t="n">
-        <v>301.7835571870698</v>
+        <v>307</v>
       </c>
       <c r="L13" t="n">
         <v>307</v>
@@ -28478,10 +28478,10 @@
         <v>307</v>
       </c>
       <c r="H15" t="n">
-        <v>304.9415831583484</v>
+        <v>307</v>
       </c>
       <c r="I15" t="n">
-        <v>201.4263858913485</v>
+        <v>199.3679690496969</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28566,7 +28566,7 @@
         <v>307</v>
       </c>
       <c r="K16" t="n">
-        <v>307</v>
+        <v>301.7835571870698</v>
       </c>
       <c r="L16" t="n">
         <v>307</v>
@@ -28593,7 +28593,7 @@
         <v>307</v>
       </c>
       <c r="T16" t="n">
-        <v>301.7835571870699</v>
+        <v>307</v>
       </c>
       <c r="U16" t="n">
         <v>307</v>
@@ -28715,10 +28715,10 @@
         <v>325.2835358750273</v>
       </c>
       <c r="H18" t="n">
-        <v>327.7640871864211</v>
+        <v>207.2286659780445</v>
       </c>
       <c r="I18" t="n">
-        <v>201.4263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28742,28 +28742,28 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>114.8712650904796</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
+        <v>190.9617972923793</v>
+      </c>
+      <c r="S18" t="n">
         <v>388</v>
       </c>
-      <c r="S18" t="n">
-        <v>355.5878892286994</v>
-      </c>
       <c r="T18" t="n">
-        <v>75.51976521751382</v>
+        <v>388</v>
       </c>
       <c r="U18" t="n">
         <v>388</v>
       </c>
       <c r="V18" t="n">
-        <v>86.51066719152016</v>
+        <v>388</v>
       </c>
       <c r="W18" t="n">
-        <v>104.3731429098285</v>
+        <v>388</v>
       </c>
       <c r="X18" t="n">
-        <v>388</v>
+        <v>91.86273944538755</v>
       </c>
       <c r="Y18" t="n">
         <v>388</v>
@@ -28779,7 +28779,7 @@
         <v>388</v>
       </c>
       <c r="C19" t="n">
-        <v>272.7252466480447</v>
+        <v>388</v>
       </c>
       <c r="D19" t="n">
         <v>388</v>
@@ -28788,22 +28788,22 @@
         <v>388</v>
       </c>
       <c r="F19" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G19" t="n">
+        <v>244.6615777595628</v>
+      </c>
+      <c r="H19" t="n">
+        <v>225.3721752819465</v>
+      </c>
+      <c r="I19" t="n">
         <v>388</v>
-      </c>
-      <c r="G19" t="n">
-        <v>388</v>
-      </c>
-      <c r="H19" t="n">
-        <v>388</v>
-      </c>
-      <c r="I19" t="n">
-        <v>277.6355097328902</v>
       </c>
       <c r="J19" t="n">
         <v>8.240686540825806</v>
       </c>
       <c r="K19" t="n">
-        <v>244.105036096225</v>
+        <v>388</v>
       </c>
       <c r="L19" t="n">
         <v>388</v>
@@ -28827,7 +28827,7 @@
         <v>388</v>
       </c>
       <c r="S19" t="n">
-        <v>388</v>
+        <v>355.7111190471177</v>
       </c>
       <c r="T19" t="n">
         <v>208.3911238833069</v>
@@ -28836,7 +28836,7 @@
         <v>150.9375388154415</v>
       </c>
       <c r="V19" t="n">
-        <v>199.1703102162162</v>
+        <v>382.0430217875447</v>
       </c>
       <c r="W19" t="n">
         <v>388</v>
@@ -28845,7 +28845,7 @@
         <v>388</v>
       </c>
       <c r="Y19" t="n">
-        <v>388</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="20">
@@ -28937,13 +28937,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>33.09991244551929</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>68.42764895589556</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
@@ -28955,7 +28955,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>201.4263858913485</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28994,10 +28994,10 @@
         <v>388</v>
       </c>
       <c r="V21" t="n">
-        <v>270.8087947155028</v>
+        <v>388</v>
       </c>
       <c r="W21" t="n">
-        <v>104.3731429098285</v>
+        <v>388</v>
       </c>
       <c r="X21" t="n">
         <v>388</v>
@@ -29013,13 +29013,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>388</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C22" t="n">
-        <v>388</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D22" t="n">
-        <v>359.9035208213979</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E22" t="n">
         <v>280.9809048369565</v>
@@ -29028,13 +29028,13 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G22" t="n">
-        <v>244.6615777595628</v>
+        <v>388</v>
       </c>
       <c r="H22" t="n">
         <v>225.3721752819465</v>
       </c>
       <c r="I22" t="n">
-        <v>165.1367998824134</v>
+        <v>388</v>
       </c>
       <c r="J22" t="n">
         <v>8.240686540825806</v>
@@ -29064,13 +29064,13 @@
         <v>388</v>
       </c>
       <c r="S22" t="n">
-        <v>355.7111190471177</v>
+        <v>388</v>
       </c>
       <c r="T22" t="n">
         <v>388</v>
       </c>
       <c r="U22" t="n">
-        <v>388</v>
+        <v>380.5723996203507</v>
       </c>
       <c r="V22" t="n">
         <v>388</v>
@@ -29082,7 +29082,7 @@
         <v>388</v>
       </c>
       <c r="Y22" t="n">
-        <v>388</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="23">
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>228.4002628749873</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -29180,10 +29180,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>325.2835358750273</v>
@@ -29234,7 +29234,7 @@
         <v>385</v>
       </c>
       <c r="W24" t="n">
-        <v>231.8795611126965</v>
+        <v>385</v>
       </c>
       <c r="X24" t="n">
         <v>385</v>
@@ -29250,7 +29250,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>287.1138003370787</v>
+        <v>385</v>
       </c>
       <c r="C25" t="n">
         <v>272.7252466480447</v>
@@ -29259,10 +29259,10 @@
         <v>385</v>
       </c>
       <c r="E25" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F25" t="n">
         <v>385</v>
-      </c>
-      <c r="F25" t="n">
-        <v>274.3828559677419</v>
       </c>
       <c r="G25" t="n">
         <v>244.6615777595628</v>
@@ -29280,7 +29280,7 @@
         <v>385</v>
       </c>
       <c r="L25" t="n">
-        <v>366.7107756987627</v>
+        <v>385</v>
       </c>
       <c r="M25" t="n">
         <v>385</v>
@@ -29304,19 +29304,19 @@
         <v>385</v>
       </c>
       <c r="T25" t="n">
-        <v>385</v>
+        <v>259.2697965181698</v>
       </c>
       <c r="U25" t="n">
-        <v>385</v>
+        <v>150.9375388154415</v>
       </c>
       <c r="V25" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W25" t="n">
-        <v>226.3728098387097</v>
+        <v>385</v>
       </c>
       <c r="X25" t="n">
-        <v>306.6079983282748</v>
+        <v>385</v>
       </c>
       <c r="Y25" t="n">
         <v>385</v>
@@ -29429,7 +29429,7 @@
         <v>307</v>
       </c>
       <c r="I27" t="n">
-        <v>201.4263858913485</v>
+        <v>199.367969049697</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>112.8128482488281</v>
+        <v>114.8712650904796</v>
       </c>
       <c r="R27" t="n">
         <v>307</v>
@@ -29502,7 +29502,7 @@
         <v>307</v>
       </c>
       <c r="G28" t="n">
-        <v>307</v>
+        <v>301.7835571870699</v>
       </c>
       <c r="H28" t="n">
         <v>307</v>
@@ -29514,7 +29514,7 @@
         <v>307</v>
       </c>
       <c r="K28" t="n">
-        <v>301.7835571870698</v>
+        <v>307</v>
       </c>
       <c r="L28" t="n">
         <v>307</v>
@@ -29666,7 +29666,7 @@
         <v>307</v>
       </c>
       <c r="I30" t="n">
-        <v>201.4263858913485</v>
+        <v>199.367969049697</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>112.8128482488281</v>
+        <v>114.8712650904796</v>
       </c>
       <c r="R30" t="n">
         <v>307</v>
@@ -29727,7 +29727,7 @@
         <v>307</v>
       </c>
       <c r="C31" t="n">
-        <v>301.7835571870698</v>
+        <v>307</v>
       </c>
       <c r="D31" t="n">
         <v>307</v>
@@ -29751,7 +29751,7 @@
         <v>307</v>
       </c>
       <c r="K31" t="n">
-        <v>307</v>
+        <v>301.7835571870698</v>
       </c>
       <c r="L31" t="n">
         <v>307</v>
@@ -29891,10 +29891,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>71.67209722189213</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>68.63624233785632</v>
       </c>
       <c r="G33" t="n">
         <v>325.2835358750273</v>
@@ -29930,10 +29930,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>247.9617972923588</v>
+        <v>423</v>
       </c>
       <c r="S33" t="n">
-        <v>187.0939999645908</v>
+        <v>423</v>
       </c>
       <c r="T33" t="n">
         <v>403.5197652175138</v>
@@ -29942,7 +29942,7 @@
         <v>400.1803597601868</v>
       </c>
       <c r="V33" t="n">
-        <v>143.5106671914997</v>
+        <v>160.11407244886</v>
       </c>
       <c r="W33" t="n">
         <v>423</v>
@@ -29951,7 +29951,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>284.939000766504</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>287.1138003370787</v>
+        <v>423</v>
       </c>
       <c r="C34" t="n">
         <v>423</v>
@@ -29982,16 +29982,16 @@
         <v>225.3721752819465</v>
       </c>
       <c r="I34" t="n">
-        <v>423</v>
+        <v>165.1367998824134</v>
       </c>
       <c r="J34" t="n">
-        <v>126.0006115506925</v>
+        <v>8.240686540825806</v>
       </c>
       <c r="K34" t="n">
-        <v>423</v>
+        <v>244.105036096225</v>
       </c>
       <c r="L34" t="n">
-        <v>423</v>
+        <v>366.7107756987627</v>
       </c>
       <c r="M34" t="n">
         <v>423</v>
@@ -30018,19 +30018,19 @@
         <v>208.3911238833069</v>
       </c>
       <c r="U34" t="n">
-        <v>150.9375388154415</v>
+        <v>421.9375388154621</v>
       </c>
       <c r="V34" t="n">
-        <v>199.1703102162162</v>
+        <v>423</v>
       </c>
       <c r="W34" t="n">
-        <v>226.3728098387097</v>
+        <v>423</v>
       </c>
       <c r="X34" t="n">
-        <v>423</v>
+        <v>341.9988808745753</v>
       </c>
       <c r="Y34" t="n">
-        <v>423</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="35">
@@ -30125,7 +30125,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>213.9376868976731</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30134,13 +30134,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.2835358750273</v>
+        <v>191.2835358749978</v>
       </c>
       <c r="H36" t="n">
         <v>327.7640871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>67.42638589131894</v>
+        <v>169.6053911840951</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,10 +30164,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>114.8712650904796</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>410.3077402022966</v>
+        <v>423</v>
       </c>
       <c r="S36" t="n">
         <v>324.0939999645818</v>
@@ -30207,13 +30207,13 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E37" t="n">
-        <v>414.9809048369861</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
-        <v>244.6615777595628</v>
+        <v>316.9582120440953</v>
       </c>
       <c r="H37" t="n">
         <v>225.3721752819465</v>
@@ -30225,7 +30225,7 @@
         <v>8.240686540825806</v>
       </c>
       <c r="K37" t="n">
-        <v>378.1050360962547</v>
+        <v>244.105036096225</v>
       </c>
       <c r="L37" t="n">
         <v>423</v>
@@ -30249,22 +30249,22 @@
         <v>423</v>
       </c>
       <c r="S37" t="n">
-        <v>423</v>
+        <v>355.7111190471177</v>
       </c>
       <c r="T37" t="n">
-        <v>208.3911238833069</v>
+        <v>342.3911238833365</v>
       </c>
       <c r="U37" t="n">
-        <v>155.9452921470918</v>
+        <v>150.9375388154415</v>
       </c>
       <c r="V37" t="n">
-        <v>199.1703102162162</v>
+        <v>333.1703102162458</v>
       </c>
       <c r="W37" t="n">
-        <v>360.3728098387393</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>381.4436454301372</v>
       </c>
       <c r="Y37" t="n">
         <v>287.4653528494624</v>
@@ -30374,7 +30374,7 @@
         <v>325.2835358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>197.0370924437491</v>
+        <v>327.7640871864211</v>
       </c>
       <c r="I39" t="n">
         <v>201.4263858913485</v>
@@ -30404,10 +30404,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>423</v>
+        <v>384.9617972923502</v>
       </c>
       <c r="S39" t="n">
-        <v>423</v>
+        <v>330.3112079649777</v>
       </c>
       <c r="T39" t="n">
         <v>403.5197652175138</v>
@@ -30450,22 +30450,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
-        <v>244.6615777595628</v>
+        <v>378.661577759592</v>
       </c>
       <c r="H40" t="n">
-        <v>225.3721752819465</v>
+        <v>359.3721752819757</v>
       </c>
       <c r="I40" t="n">
-        <v>165.1367998824134</v>
+        <v>299.1367998824425</v>
       </c>
       <c r="J40" t="n">
-        <v>8.240686540825806</v>
+        <v>136.826545126597</v>
       </c>
       <c r="K40" t="n">
-        <v>378.1050360962542</v>
+        <v>244.105036096225</v>
       </c>
       <c r="L40" t="n">
-        <v>423</v>
+        <v>366.7107756987627</v>
       </c>
       <c r="M40" t="n">
         <v>423</v>
@@ -30489,16 +30489,16 @@
         <v>355.7111190471177</v>
       </c>
       <c r="T40" t="n">
-        <v>342.391123883336</v>
+        <v>208.3911238833069</v>
       </c>
       <c r="U40" t="n">
-        <v>223.2341730999755</v>
+        <v>150.9375388154415</v>
       </c>
       <c r="V40" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>360.3728098387388</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>197.0000000000458</v>
+        <v>197</v>
       </c>
       <c r="S41" t="n">
         <v>197</v>
@@ -34755,7 +34755,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>55.26566379245642</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>73.34857263696284</v>
@@ -34764,7 +34764,7 @@
         <v>122.2691811653487</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>55.26566379245642</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34825,22 +34825,22 @@
         <v>134</v>
       </c>
       <c r="K3" t="n">
+        <v>134</v>
+      </c>
+      <c r="L3" t="n">
+        <v>134</v>
+      </c>
+      <c r="M3" t="n">
         <v>128.5858585858587</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34883,31 +34883,31 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H4" t="n">
         <v>134</v>
       </c>
       <c r="I4" t="n">
+        <v>51.0077533317391</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>134</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>33.28922430123725</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>44.28888095288227</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -34943,7 +34943,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>22.50493260915607</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,7 +34980,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>92.5572706126927</v>
+        <v>37.29160682023632</v>
       </c>
       <c r="K5" t="n">
         <v>108.4108341708543</v>
@@ -34989,7 +34989,7 @@
         <v>134</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>55.26566379245642</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -35068,13 +35068,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>128.5858585858587</v>
+        <v>134</v>
       </c>
       <c r="N6" t="n">
         <v>134</v>
       </c>
       <c r="O6" t="n">
-        <v>134</v>
+        <v>128.5858585858587</v>
       </c>
       <c r="P6" t="n">
         <v>134</v>
@@ -35132,16 +35132,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>4.196613144875293</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>134</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>33.28922430123723</v>
@@ -35302,16 +35302,16 @@
         <v>191</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>14.99222204515247</v>
-      </c>
-      <c r="M9" t="n">
-        <v>191</v>
       </c>
       <c r="N9" t="n">
         <v>191</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>130.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>117.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>122.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>128.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>158.3384222404372</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>177.6278247180535</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>64.41021299084227</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>36.28922430123725</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,7 +35405,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>26.48720697766789</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -35420,7 +35420,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>115.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,16 +35457,16 @@
         <v>328</v>
       </c>
       <c r="K11" t="n">
+        <v>108.4108341708543</v>
+      </c>
+      <c r="L11" t="n">
         <v>328.0000000000001</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>328</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
-        <v>119.1297209451631</v>
+        <v>10.71888677430881</v>
       </c>
       <c r="O11" t="n">
         <v>73.34857263696284</v>
@@ -35533,13 +35533,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>168.2906062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>264.7378546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>314.2908779596624</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>202.4900421645042</v>
@@ -35548,7 +35548,7 @@
         <v>253.2245501086549</v>
       </c>
       <c r="O12" t="n">
-        <v>328</v>
+        <v>209.2624170811954</v>
       </c>
       <c r="P12" t="n">
         <v>200.7420045146532</v>
@@ -35588,7 +35588,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.88619966292134</v>
+        <v>14.66975684999124</v>
       </c>
       <c r="C13" t="n">
         <v>34.27475335195533</v>
@@ -35615,7 +35615,7 @@
         <v>298.7593134591742</v>
       </c>
       <c r="K13" t="n">
-        <v>57.67852109084476</v>
+        <v>62.89496390377498</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,16 +35691,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>328</v>
+        <v>37.29160682023632</v>
       </c>
       <c r="K14" t="n">
-        <v>108.4108341708543</v>
+        <v>275.3448879942736</v>
       </c>
       <c r="L14" t="n">
         <v>134.4932261306533</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="N14" t="n">
         <v>328</v>
@@ -35712,7 +35712,7 @@
         <v>122.2691811653487</v>
       </c>
       <c r="Q14" t="n">
-        <v>204.2256606436557</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35770,13 +35770,13 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>168.2906062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>187.0328824743156</v>
+        <v>264.7378546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>202.4900421645042</v>
@@ -35785,10 +35785,10 @@
         <v>253.2245501086549</v>
       </c>
       <c r="O15" t="n">
-        <v>328</v>
+        <v>209.2624170811954</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>200.7420045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>298.7593134591742</v>
       </c>
       <c r="K16" t="n">
-        <v>62.89496390377496</v>
+        <v>57.67852109084476</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>93.39243330376299</v>
+        <v>98.6088761166931</v>
       </c>
       <c r="U16" t="n">
         <v>156.0624611845585</v>
@@ -35928,7 +35928,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>37.29160682023632</v>
+        <v>328</v>
       </c>
       <c r="K17" t="n">
         <v>108.4108341708543</v>
@@ -35937,10 +35937,10 @@
         <v>134.4932261306533</v>
       </c>
       <c r="M17" t="n">
-        <v>328</v>
+        <v>204.2256606436556</v>
       </c>
       <c r="N17" t="n">
-        <v>166.9340538234194</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>73.34857263696284</v>
@@ -36007,13 +36007,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>168.2906062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>187.0328824743156</v>
+        <v>264.7378546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>202.4900421645042</v>
@@ -36022,10 +36022,10 @@
         <v>253.2245501086549</v>
       </c>
       <c r="O18" t="n">
-        <v>328</v>
+        <v>209.2624170811954</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>200.7420045146532</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36065,7 +36065,7 @@
         <v>100.8861996629213</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>115.2747533519553</v>
       </c>
       <c r="D19" t="n">
         <v>102.4637819444445</v>
@@ -36074,22 +36074,22 @@
         <v>107.0190951630435</v>
       </c>
       <c r="F19" t="n">
-        <v>113.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>143.3384222404372</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>162.6278247180535</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>112.4987098504769</v>
+        <v>222.8632001175866</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>143.894963903775</v>
       </c>
       <c r="L19" t="n">
         <v>21.28922430123725</v>
@@ -36113,7 +36113,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>32.28888095288227</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -36122,7 +36122,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>182.8727115713286</v>
       </c>
       <c r="W19" t="n">
         <v>161.6271901612903</v>
@@ -36131,7 +36131,7 @@
         <v>140.5563545698924</v>
       </c>
       <c r="Y19" t="n">
-        <v>100.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>328</v>
+        <v>37.29160682023632</v>
       </c>
       <c r="K20" t="n">
-        <v>180.2542486168215</v>
+        <v>108.4108341708543</v>
       </c>
       <c r="L20" t="n">
         <v>134.4932261306533</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>166.9340538234194</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="O20" t="n">
+        <v>73.34857263696284</v>
+      </c>
+      <c r="P20" t="n">
+        <v>122.2691811653487</v>
+      </c>
+      <c r="Q20" t="n">
         <v>328</v>
-      </c>
-      <c r="P20" t="n">
-        <v>328</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,7 +36244,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>168.2906062376757</v>
       </c>
       <c r="K21" t="n">
         <v>264.7378546407913</v>
@@ -36256,7 +36256,7 @@
         <v>202.4900421645042</v>
       </c>
       <c r="N21" t="n">
-        <v>175.5195779421791</v>
+        <v>7.228971704503375</v>
       </c>
       <c r="O21" t="n">
         <v>328</v>
@@ -36299,13 +36299,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>100.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>115.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>74.36730276584247</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -36314,13 +36314,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>143.3384222404372</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>222.8632001175866</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -36350,13 +36350,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>32.28888095288227</v>
       </c>
       <c r="T22" t="n">
         <v>179.6088761166931</v>
       </c>
       <c r="U22" t="n">
-        <v>237.0624611845585</v>
+        <v>229.6348608049092</v>
       </c>
       <c r="V22" t="n">
         <v>188.8296897837838</v>
@@ -36368,7 +36368,7 @@
         <v>140.5563545698924</v>
       </c>
       <c r="Y22" t="n">
-        <v>100.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -36402,28 +36402,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>37.29160682023632</v>
+        <v>405.0000000000152</v>
       </c>
       <c r="K23" t="n">
-        <v>108.4108341708543</v>
+        <v>108.4108341708542</v>
       </c>
       <c r="L23" t="n">
-        <v>134.4932261306533</v>
+        <v>405</v>
       </c>
       <c r="M23" t="n">
-        <v>317.8229427122778</v>
+        <v>206.8769568285163</v>
       </c>
       <c r="N23" t="n">
-        <v>405.0000000000152</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>73.34857263696284</v>
       </c>
       <c r="P23" t="n">
-        <v>122.2691811653487</v>
+        <v>405.0000000000152</v>
       </c>
       <c r="Q23" t="n">
-        <v>405.0000000000152</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36493,10 +36493,10 @@
         <v>202.4900421645042</v>
       </c>
       <c r="N24" t="n">
-        <v>253.2245501086549</v>
+        <v>44.32345882730577</v>
       </c>
       <c r="O24" t="n">
-        <v>141.0499306213974</v>
+        <v>349.9510219027464</v>
       </c>
       <c r="P24" t="n">
         <v>200.7420045146532</v>
@@ -36536,7 +36536,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>97.88619966292134</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -36545,10 +36545,10 @@
         <v>99.46378194444452</v>
       </c>
       <c r="E25" t="n">
-        <v>104.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>110.6171440322581</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -36566,7 +36566,7 @@
         <v>140.894963903775</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>18.28922430123723</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -36590,19 +36590,19 @@
         <v>29.28888095288227</v>
       </c>
       <c r="T25" t="n">
-        <v>176.6088761166931</v>
+        <v>50.87867263486289</v>
       </c>
       <c r="U25" t="n">
-        <v>234.0624611845585</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>158.6271901612903</v>
       </c>
       <c r="X25" t="n">
-        <v>59.1643528981672</v>
+        <v>137.5563545698924</v>
       </c>
       <c r="Y25" t="n">
         <v>97.53464715053764</v>
@@ -36648,19 +36648,19 @@
         <v>134.4932261306533</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>328.0000000000214</v>
       </c>
       <c r="N26" t="n">
-        <v>328.0000000000214</v>
+        <v>166.9340538233765</v>
       </c>
       <c r="O26" t="n">
-        <v>328.0000000000214</v>
+        <v>73.34857263696284</v>
       </c>
       <c r="P26" t="n">
         <v>122.2691811653487</v>
       </c>
       <c r="Q26" t="n">
-        <v>240.2826264603393</v>
+        <v>328.0000000000214</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36721,19 +36721,19 @@
         <v>168.2906062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>264.7378546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>328.0000000000214</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>202.4900421645042</v>
+        <v>83.7524592456783</v>
       </c>
       <c r="N27" t="n">
         <v>253.2245501086549</v>
       </c>
       <c r="O27" t="n">
-        <v>146.0002717219652</v>
+        <v>328.0000000000214</v>
       </c>
       <c r="P27" t="n">
         <v>200.7420045146532</v>
@@ -36788,7 +36788,7 @@
         <v>32.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>62.33842224043718</v>
+        <v>57.12197942750709</v>
       </c>
       <c r="H28" t="n">
         <v>81.62782471805352</v>
@@ -36800,7 +36800,7 @@
         <v>298.7593134591742</v>
       </c>
       <c r="K28" t="n">
-        <v>57.67852109084476</v>
+        <v>62.89496390377498</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36879,13 +36879,13 @@
         <v>37.29160682023632</v>
       </c>
       <c r="K29" t="n">
-        <v>108.4108341708543</v>
+        <v>275.3448879942308</v>
       </c>
       <c r="L29" t="n">
         <v>134.4932261306533</v>
       </c>
       <c r="M29" t="n">
-        <v>166.9340538233765</v>
+        <v>328.0000000000214</v>
       </c>
       <c r="N29" t="n">
         <v>328.0000000000214</v>
@@ -36897,7 +36897,7 @@
         <v>122.2691811653487</v>
       </c>
       <c r="Q29" t="n">
-        <v>328.0000000000214</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36958,10 +36958,10 @@
         <v>168.2906062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>264.7378546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>328.0000000000214</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>202.4900421645042</v>
@@ -36970,10 +36970,10 @@
         <v>253.2245501086549</v>
       </c>
       <c r="O30" t="n">
-        <v>328.0000000000214</v>
+        <v>209.2624170811954</v>
       </c>
       <c r="P30" t="n">
-        <v>18.74227623659706</v>
+        <v>200.7420045146532</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -37013,7 +37013,7 @@
         <v>19.88619966292134</v>
       </c>
       <c r="C31" t="n">
-        <v>29.0583105390252</v>
+        <v>34.27475335195533</v>
       </c>
       <c r="D31" t="n">
         <v>21.46378194444452</v>
@@ -37037,7 +37037,7 @@
         <v>298.7593134591742</v>
       </c>
       <c r="K31" t="n">
-        <v>62.89496390377496</v>
+        <v>57.67852109084476</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>98.6088761166931</v>
+        <v>98.60887611669311</v>
       </c>
       <c r="U31" t="n">
         <v>156.0624611845585</v>
@@ -37122,7 +37122,7 @@
         <v>134.4932261306533</v>
       </c>
       <c r="M32" t="n">
-        <v>55.23708412640845</v>
+        <v>271.0000000000205</v>
       </c>
       <c r="N32" t="n">
         <v>271.0000000000205</v>
@@ -37134,7 +37134,7 @@
         <v>122.2691811653487</v>
       </c>
       <c r="Q32" t="n">
-        <v>271.0000000000205</v>
+        <v>55.23708412640851</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,25 +37192,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>168.2906062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>75.33591277730491</v>
+        <v>264.7378546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>271.0000000000205</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>202.4900421645042</v>
       </c>
       <c r="N33" t="n">
-        <v>253.2245501086549</v>
+        <v>236.7899974928807</v>
       </c>
       <c r="O33" t="n">
-        <v>271.0000000000205</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>200.7420045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>135.8861996629213</v>
       </c>
       <c r="C34" t="n">
         <v>150.2747533519553</v>
@@ -37268,16 +37268,16 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>257.8632001175866</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>117.7599250098666</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>178.894963903775</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>56.28922430123725</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -37304,19 +37304,19 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>271.0000000000205</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>223.8296897837838</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>196.6271901612903</v>
       </c>
       <c r="X34" t="n">
-        <v>175.5563545698924</v>
+        <v>94.55523544446773</v>
       </c>
       <c r="Y34" t="n">
-        <v>135.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -37362,7 +37362,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>55.26566379245642</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>73.34857263696284</v>
@@ -37371,7 +37371,7 @@
         <v>122.2691811653487</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>55.26566379245642</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,25 +37429,25 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>128.5858585857698</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>134.0000000000296</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>134.0000000000296</v>
       </c>
       <c r="N36" t="n">
-        <v>128.5858585857698</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>134.0000000000296</v>
       </c>
       <c r="P36" t="n">
-        <v>134.0000000000296</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37493,13 +37493,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>134.0000000000296</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>72.2966342845325</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -37511,7 +37511,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>134.0000000000296</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>56.28922430123725</v>
@@ -37535,22 +37535,22 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>67.28888095288227</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>134.0000000000296</v>
       </c>
       <c r="U37" t="n">
-        <v>5.00775333165027</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>134.0000000000296</v>
       </c>
       <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
         <v>134.0000000000296</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -37599,7 +37599,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>55.26566379245642</v>
       </c>
       <c r="O38" t="n">
         <v>73.34857263696284</v>
@@ -37608,7 +37608,7 @@
         <v>122.2691811653487</v>
       </c>
       <c r="Q38" t="n">
-        <v>55.26566379245642</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,25 +37666,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>134.0000000000291</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>134.0000000000291</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
-        <v>134.0000000000291</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>128.5858585857711</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>134.0000000000291</v>
       </c>
       <c r="P39" t="n">
-        <v>134.0000000000291</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37736,22 +37736,22 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>134.0000000000291</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>134.0000000000291</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>134.0000000000291</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>128.5858585857711</v>
       </c>
       <c r="K40" t="n">
-        <v>134.0000000000291</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>56.28922430123725</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37775,16 +37775,16 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>134.0000000000291</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>72.29663428453391</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>134.0000000000291</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -37903,22 +37903,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>134.0000000000528</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>128.5858585857002</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>134.0000000000528</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>134.0000000000528</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>128.5858585857002</v>
       </c>
       <c r="P42" t="n">
         <v>134.0000000000528</v>
@@ -38070,10 +38070,10 @@
         <v>134</v>
       </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>55.26566379245642</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>73.34857263696284</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>134.0000000000819</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" t="n">
+        <v>128.585858585613</v>
+      </c>
+      <c r="N45" t="n">
         <v>134.0000000000819</v>
       </c>
-      <c r="N45" t="n">
-        <v>128.585858585613</v>
-      </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>134.0000000000819</v>
       </c>
       <c r="P45" t="n">
-        <v>134.0000000000819</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38216,7 +38216,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>31.86320011758665</v>
+        <v>31.86320011758664</v>
       </c>
       <c r="J46" t="n">
         <v>134.0000000000819</v>
